--- a/2026/YRIGOYEN 7630/ENERO/YRIGOYEN7630-Enero.xlsx
+++ b/2026/YRIGOYEN 7630/ENERO/YRIGOYEN7630-Enero.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\YRIGOYEN 7630\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A048CDE9-8B48-4207-92AD-B3AF554C812B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EC4CCF-1854-42D2-89D6-32CAEF3959DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$120</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$121</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -308,9 +308,6 @@
     <t>Mantenimiento de cuenta</t>
   </si>
   <si>
-    <t>Subidos en Agost000</t>
-  </si>
-  <si>
     <t>Federacion patronal - Seguro de vida Poliza nro. 211840604</t>
   </si>
   <si>
@@ -320,39 +317,9 @@
     <t>Ascensores lema - Mantenimiento agosto</t>
   </si>
   <si>
-    <t>Transf 18/12</t>
-  </si>
-  <si>
     <t>Debito 01/12</t>
   </si>
   <si>
-    <t>Debito 02/12</t>
-  </si>
-  <si>
-    <t>Debito 09/12</t>
-  </si>
-  <si>
-    <t>Debito 12/12</t>
-  </si>
-  <si>
-    <t>Kromacolor - Materiales para terraza</t>
-  </si>
-  <si>
-    <t>Debito 16/12</t>
-  </si>
-  <si>
-    <t>Transf 05/12</t>
-  </si>
-  <si>
-    <t>Balcazza Leonardo - Resto terraza</t>
-  </si>
-  <si>
-    <t>Dpto. 10 - Materiales - Arreglo perdida caño cloacal - Pago el dpto 10</t>
-  </si>
-  <si>
-    <t>Julio Doartero - Trabajo de plomeria en destapacion</t>
-  </si>
-  <si>
     <t>Transf 30/12</t>
   </si>
   <si>
@@ -374,7 +341,43 @@
     <t>Fumigacion mes de ENERO</t>
   </si>
   <si>
-    <t>Honorarios administracion - DICIEMBRE - Se debe ENERO</t>
+    <t>Subidos en En3r0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honorarios administracion - DICIEMBRE </t>
+  </si>
+  <si>
+    <t>Honorarios administracion - ENERO</t>
+  </si>
+  <si>
+    <t>Debito 5/1</t>
+  </si>
+  <si>
+    <t>Debito 12/01</t>
+  </si>
+  <si>
+    <t>Debito 13/01</t>
+  </si>
+  <si>
+    <t>Debito 09/01</t>
+  </si>
+  <si>
+    <t>Servicio de fumigacion - Sra. Gladys</t>
+  </si>
+  <si>
+    <t>Transf 09/01</t>
+  </si>
+  <si>
+    <t>Cuello Natalia - Destapacion dpto 9</t>
+  </si>
+  <si>
+    <t>Cuello Natalia - Destapacion dpto 3</t>
+  </si>
+  <si>
+    <t>Cuota 1 de 2 - trabajo de pintura dpto 10</t>
+  </si>
+  <si>
+    <t>Abonado Sra. Ana Maria Castro</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1088,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1192,7 +1195,6 @@
     </xf>
     <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1332,6 +1334,13 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="23" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1340,8 +1349,21 @@
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1354,22 +1376,25 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1387,12 +1412,6 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1407,15 +1426,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1782,22 +1792,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M124"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M125"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="15"/>
       <c r="B1" s="71" t="s">
         <v>55</v>
@@ -1806,7 +1816,7 @@
       <c r="D1" s="71"/>
       <c r="E1" s="72"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" s="73" t="s">
         <v>28</v>
@@ -1815,32 +1825,32 @@
       <c r="D2" s="73"/>
       <c r="E2" s="74"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
-      <c r="B3" s="188" t="s">
+      <c r="B3" s="193" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
-      <c r="E3" s="189"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="193"/>
+      <c r="D3" s="193"/>
+      <c r="E3" s="194"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="101" t="s">
+      <c r="B4" s="100" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>57</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="73" t="s">
@@ -1848,7 +1858,7 @@
       </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>56</v>
       </c>
@@ -1859,57 +1869,57 @@
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="193" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" s="193"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="193"/>
-      <c r="C9" s="193"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="193"/>
-      <c r="C10" s="193"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="192" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="196" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="196"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="196"/>
+      <c r="C9" s="196"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="196"/>
+      <c r="C10" s="196"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="195" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="192"/>
-      <c r="C13" s="192"/>
-      <c r="D13" s="192"/>
-      <c r="E13" s="192"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="192"/>
-      <c r="B14" s="192"/>
-      <c r="C14" s="192"/>
-      <c r="D14" s="192"/>
-      <c r="E14" s="192"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="192"/>
-      <c r="B15" s="192"/>
-      <c r="C15" s="192"/>
-      <c r="D15" s="192"/>
-      <c r="E15" s="192"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="192"/>
-      <c r="B16" s="192"/>
-      <c r="C16" s="192"/>
-      <c r="D16" s="192"/>
-      <c r="E16" s="192"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="195"/>
+      <c r="C13" s="195"/>
+      <c r="D13" s="195"/>
+      <c r="E13" s="195"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="195"/>
+      <c r="B14" s="195"/>
+      <c r="C14" s="195"/>
+      <c r="D14" s="195"/>
+      <c r="E14" s="195"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="195"/>
+      <c r="B15" s="195"/>
+      <c r="C15" s="195"/>
+      <c r="D15" s="195"/>
+      <c r="E15" s="195"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="195"/>
+      <c r="B16" s="195"/>
+      <c r="C16" s="195"/>
+      <c r="D16" s="195"/>
+      <c r="E16" s="195"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>10</v>
       </c>
@@ -1918,7 +1928,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
         <v>35</v>
       </c>
@@ -1927,950 +1937,961 @@
       <c r="D21" s="35"/>
       <c r="E21" s="35"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="159">
-        <v>796657</v>
+      <c r="D22" s="158">
+        <v>871845</v>
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="159"/>
+      <c r="D23" s="158"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="59" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="59"/>
       <c r="C24" s="59"/>
-      <c r="D24" s="168">
+      <c r="D24" s="167">
         <f>SUM(D22:D23)</f>
-        <v>796657</v>
-      </c>
-      <c r="E24" s="143"/>
+        <v>871845</v>
+      </c>
+      <c r="E24" s="142"/>
       <c r="G24" s="22"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="159"/>
+      <c r="D25" s="158"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="29"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="159"/>
+      <c r="D26" s="158"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="159"/>
+      <c r="D27" s="158"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="169"/>
+      <c r="D28" s="168"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="169">
-        <v>490846</v>
-      </c>
+      <c r="D29" s="168"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="59" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="59"/>
       <c r="C30" s="59"/>
-      <c r="D30" s="170">
+      <c r="D30" s="169">
         <f>SUM(D25:D29)</f>
-        <v>490846</v>
-      </c>
-      <c r="E30" s="143"/>
-    </row>
-    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="E30" s="142"/>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="30" t="s">
         <v>1</v>
       </c>
       <c r="B31" s="30"/>
       <c r="C31" s="30"/>
-      <c r="D31" s="171"/>
-      <c r="E31" s="144">
+      <c r="D31" s="170"/>
+      <c r="E31" s="143">
         <f>D24+D30</f>
-        <v>1287503</v>
+        <v>871845</v>
       </c>
       <c r="F31" s="22"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="36" t="s">
         <v>19</v>
       </c>
       <c r="B32" s="36"/>
       <c r="C32" s="36"/>
-      <c r="D32" s="172"/>
-      <c r="E32" s="145"/>
-    </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="186" t="s">
-        <v>112</v>
-      </c>
-      <c r="B33" s="187"/>
+      <c r="D32" s="171"/>
+      <c r="E32" s="144"/>
+    </row>
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="191" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" s="192"/>
       <c r="C33" s="54"/>
-      <c r="D33" s="159">
+      <c r="D33" s="158">
         <v>35000</v>
       </c>
-      <c r="E33" s="146"/>
-    </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="186" t="s">
-        <v>115</v>
-      </c>
-      <c r="B34" s="187"/>
+      <c r="E33" s="145"/>
+    </row>
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="179" t="s">
+        <v>105</v>
+      </c>
+      <c r="B34" s="180"/>
       <c r="C34" s="54"/>
-      <c r="D34" s="180">
-        <v>112400</v>
-      </c>
-      <c r="E34" s="146"/>
-      <c r="H34" s="157" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="30" t="s">
+      <c r="D34" s="158">
+        <v>112000</v>
+      </c>
+      <c r="E34" s="145"/>
+    </row>
+    <row r="35" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="191" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" s="192"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="182">
+        <v>147300</v>
+      </c>
+      <c r="E35" s="145"/>
+      <c r="H35" s="156" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="30" t="s">
         <v>16</v>
-      </c>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="173"/>
-      <c r="E35" s="147">
-        <f>SUM(D33:D34)</f>
-        <v>147400</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="36" t="s">
-        <v>32</v>
       </c>
       <c r="B36" s="30"/>
       <c r="C36" s="30"/>
-      <c r="D36" s="174"/>
-      <c r="E36" s="148"/>
-    </row>
-    <row r="37" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="190" t="s">
+      <c r="D36" s="172"/>
+      <c r="E36" s="146">
+        <f>SUM(D33:D35)</f>
+        <v>294300</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="173"/>
+      <c r="E37" s="147"/>
+    </row>
+    <row r="38" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="189" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" s="190"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="183">
+        <f>6696+26570</f>
+        <v>33266</v>
+      </c>
+      <c r="E38" s="181" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="191" t="s">
         <v>94</v>
       </c>
-      <c r="B37" s="191"/>
-      <c r="C37" s="56"/>
-      <c r="D37" s="181">
-        <f>26570+6696</f>
-        <v>33266</v>
-      </c>
-      <c r="E37" s="160" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="186" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" s="187"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="182">
+      <c r="B39" s="192"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="184">
         <v>54278</v>
       </c>
-      <c r="E38" s="149" t="str">
-        <f>E37</f>
-        <v>Debito 02/12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="30" t="s">
+      <c r="E39" s="148" t="str">
+        <f>E38</f>
+        <v>Debito 5/1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="173"/>
-      <c r="E39" s="150">
-        <f>SUM(D37:D38)</f>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="172"/>
+      <c r="E40" s="149">
+        <f>SUM(D38:D39)</f>
         <v>87544</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="36" t="s">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B40" s="151"/>
-      <c r="C40" s="151"/>
-      <c r="D40" s="175"/>
-      <c r="E40" s="152"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
+      <c r="B41" s="150"/>
+      <c r="C41" s="150"/>
+      <c r="D41" s="174"/>
+      <c r="E41" s="151"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="184">
-        <v>937097.26</v>
-      </c>
-      <c r="E41" s="160" t="s">
-        <v>100</v>
-      </c>
-      <c r="G41" s="127"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="54"/>
-      <c r="D42" s="183">
-        <v>10602.27</v>
-      </c>
-      <c r="E42" s="160" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D42" s="185">
+        <v>937097.26</v>
+      </c>
+      <c r="E42" s="159" t="s">
+        <v>108</v>
+      </c>
+      <c r="G42" s="126"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="54"/>
-      <c r="D43" s="183">
+      <c r="D43" s="185">
+        <v>10602.27</v>
+      </c>
+      <c r="E43" s="159" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="185">
         <v>75532.289999999994</v>
       </c>
-      <c r="E43" s="160" t="str">
-        <f>E42</f>
-        <v>Debito 16/12</v>
-      </c>
-      <c r="G43" s="142"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="185">
-        <v>132242.74</v>
-      </c>
-      <c r="E44" s="160" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="str">
-        <f>A44</f>
-        <v>Sindicatos mes de ENERO</v>
+      <c r="E44" s="159" t="str">
+        <f>E43</f>
+        <v>Debito 13/01</v>
+      </c>
+      <c r="F44" s="45">
+        <f>D44+D43</f>
+        <v>86134.56</v>
+      </c>
+      <c r="G44" s="141"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="185">
-        <v>8554.83</v>
-      </c>
-      <c r="E45" s="161" t="str">
-        <f>E44</f>
-        <v>Debito 12/12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D45" s="162">
+        <v>132242.74</v>
+      </c>
+      <c r="E45" s="159" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="str">
         <f>A45</f>
         <v>Sindicatos mes de ENERO</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
-      <c r="D46" s="185">
+      <c r="D46" s="162">
+        <v>8554.83</v>
+      </c>
+      <c r="E46" s="160" t="str">
+        <f>E45</f>
+        <v>Debito 13/01</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="str">
+        <f>A46</f>
+        <v>Sindicatos mes de ENERO</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="162">
         <v>76993.429999999993</v>
       </c>
-      <c r="E46" s="162" t="str">
-        <f>E45</f>
-        <v>Debito 12/12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="30" t="s">
+      <c r="E47" s="161" t="str">
+        <f>E46</f>
+        <v>Debito 13/01</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B47" s="151"/>
-      <c r="C47" s="151"/>
-      <c r="D47" s="176"/>
-      <c r="E47" s="150">
-        <f>SUM(D41:D46)</f>
+      <c r="B48" s="150"/>
+      <c r="C48" s="150"/>
+      <c r="D48" s="175"/>
+      <c r="E48" s="149">
+        <f>SUM(D42:D47)</f>
         <v>1241022.82</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="36" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B48" s="151"/>
-      <c r="C48" s="151"/>
-      <c r="D48" s="175"/>
-      <c r="E48" s="152"/>
-    </row>
-    <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
+      <c r="B49" s="150"/>
+      <c r="C49" s="150"/>
+      <c r="D49" s="174"/>
+      <c r="E49" s="151"/>
+    </row>
+    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="163">
-        <v>67167.600000000006</v>
-      </c>
-      <c r="E49" s="160" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="162">
+        <v>81386.33</v>
+      </c>
+      <c r="E50" s="159" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B50" s="163"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="163">
-        <v>28837.72</v>
-      </c>
-      <c r="E50" s="160" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
+      <c r="B51" s="162"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="162">
+        <v>38806.65</v>
+      </c>
+      <c r="E51" s="159" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="185">
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="162">
         <v>26145.55</v>
       </c>
-      <c r="E51" s="160" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="190" t="s">
+      <c r="E52" s="159" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="189" t="s">
         <v>77</v>
       </c>
-      <c r="B52" s="191"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="185">
-        <v>366845.76</v>
-      </c>
-      <c r="E52" s="160" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="30" t="s">
+      <c r="B53" s="190"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="162">
+        <v>377536.65</v>
+      </c>
+      <c r="E53" s="159" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="177"/>
-      <c r="E53" s="150">
-        <f>SUM(D49:D52)</f>
-        <v>488996.63</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="36"/>
       <c r="B54" s="30"/>
       <c r="C54" s="30"/>
-      <c r="D54" s="173"/>
-      <c r="E54" s="153"/>
-    </row>
-    <row r="55" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="165" t="s">
-        <v>96</v>
-      </c>
-      <c r="B55" s="158"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="185">
+      <c r="D54" s="176"/>
+      <c r="E54" s="149">
+        <f>SUM(D50:D53)</f>
+        <v>523875.18000000005</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="36"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="172"/>
+      <c r="E55" s="152"/>
+    </row>
+    <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="164" t="s">
+        <v>95</v>
+      </c>
+      <c r="B56" s="157"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="162">
         <v>85000</v>
       </c>
-      <c r="E55" s="164" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="165" t="s">
+      <c r="E56" s="163" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="164" t="s">
+        <v>103</v>
+      </c>
+      <c r="B57" s="157"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="162">
+        <v>45000</v>
+      </c>
+      <c r="E57" s="163" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="164" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" s="157"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="108">
+        <v>340000</v>
+      </c>
+      <c r="E58" s="186" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="164" t="s">
+        <v>113</v>
+      </c>
+      <c r="B59" s="157"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="108">
+        <v>59600</v>
+      </c>
+      <c r="E59" s="163" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="189" t="s">
         <v>114</v>
       </c>
-      <c r="B56" s="158"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="185">
+      <c r="B60" s="190"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="108">
+        <v>35500</v>
+      </c>
+      <c r="E60" s="163" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="189" t="s">
+        <v>111</v>
+      </c>
+      <c r="B61" s="190"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="108">
         <v>45000</v>
       </c>
-      <c r="E56" s="164" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="165" t="s">
-        <v>105</v>
-      </c>
-      <c r="B57" s="158"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="109">
-        <v>600000</v>
-      </c>
-      <c r="E57" s="164" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="190" t="s">
-        <v>106</v>
-      </c>
-      <c r="B58" s="191"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="109">
-        <v>220000</v>
-      </c>
-      <c r="E58" s="164"/>
-    </row>
-    <row r="59" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="165" t="s">
-        <v>102</v>
-      </c>
-      <c r="B59" s="158"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="109">
-        <v>19726.189999999999</v>
-      </c>
-      <c r="E59" s="164" t="s">
+      <c r="E61" s="163" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="190" t="s">
-        <v>107</v>
-      </c>
-      <c r="B60" s="191"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="109">
-        <v>85000</v>
-      </c>
-      <c r="E60" s="164" t="s">
-        <v>108</v>
-      </c>
-      <c r="I60" s="190"/>
-      <c r="J60" s="191"/>
-    </row>
-    <row r="61" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="30" t="s">
+    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="35"/>
-      <c r="E61" s="154">
-        <f>SUM(D55:D60)</f>
-        <v>1054726.19</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="36" t="s">
+      <c r="B62" s="36"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="153">
+        <f>SUM(D56:D61)</f>
+        <v>610100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B62" s="69"/>
-      <c r="C62" s="30"/>
-      <c r="D62" s="171"/>
-      <c r="E62" s="153"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="5" t="s">
+      <c r="B63" s="69"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="170"/>
+      <c r="E63" s="152"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="163">
-        <v>53000</v>
-      </c>
-      <c r="E63" s="155"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
-      <c r="D64" s="163">
-        <f>56953.55+12000</f>
-        <v>68953.55</v>
-      </c>
-      <c r="E64" s="41"/>
-    </row>
-    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="53" t="s">
+      <c r="D64" s="162">
+        <v>53000</v>
+      </c>
+      <c r="E64" s="154"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="162">
+        <v>88932.56</v>
+      </c>
+      <c r="E65" s="41"/>
+    </row>
+    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="B65" s="53"/>
-      <c r="C65" s="53"/>
-      <c r="D65" s="112"/>
-      <c r="E65" s="106">
-        <f>SUM(D63:D64)</f>
-        <v>121953.55</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="105"/>
-      <c r="E66" s="113"/>
-    </row>
-    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="31" t="s">
+      <c r="B66" s="53"/>
+      <c r="C66" s="53"/>
+      <c r="D66" s="111"/>
+      <c r="E66" s="105">
+        <f>SUM(D64:D65)</f>
+        <v>141932.56</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="5"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="104"/>
+      <c r="E67" s="112"/>
+    </row>
+    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="B67" s="31"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="114"/>
-      <c r="E67" s="115"/>
-    </row>
-    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="1"/>
-      <c r="D68" s="116"/>
-      <c r="E68" s="117"/>
-      <c r="F68" s="45"/>
-    </row>
-    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="s">
+      <c r="B68" s="31"/>
+      <c r="C68" s="31"/>
+      <c r="D68" s="113"/>
+      <c r="E68" s="114"/>
+    </row>
+    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="1"/>
+      <c r="D69" s="115"/>
+      <c r="E69" s="116"/>
+      <c r="F69" s="45"/>
+    </row>
+    <row r="70" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B69" s="10"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="118"/>
-      <c r="E69" s="119">
-        <f>(SUM(E27:E67))</f>
-        <v>4429146.1900000004</v>
-      </c>
-      <c r="F69" s="142"/>
-      <c r="G69" s="45"/>
-      <c r="H69" s="127"/>
-      <c r="I69" s="127"/>
-      <c r="J69" s="127"/>
-      <c r="K69" s="127"/>
-      <c r="L69" s="127"/>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D70" s="116"/>
-      <c r="E70" s="116"/>
-      <c r="H70" s="127"/>
-      <c r="I70" s="127"/>
-      <c r="J70" s="127"/>
-      <c r="K70" s="127"/>
-      <c r="L70" s="127"/>
-    </row>
-    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D71" s="116"/>
-      <c r="E71" s="116"/>
-      <c r="H71" s="178"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" s="11" t="s">
+      <c r="B70" s="10"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="117"/>
+      <c r="E70" s="118">
+        <f>(SUM(E27:E68))</f>
+        <v>3770619.5600000005</v>
+      </c>
+      <c r="F70" s="141"/>
+      <c r="G70" s="45"/>
+      <c r="H70" s="126"/>
+      <c r="I70" s="126"/>
+      <c r="J70" s="126"/>
+      <c r="K70" s="126"/>
+      <c r="L70" s="126"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D71" s="115"/>
+      <c r="E71" s="115"/>
+      <c r="H71" s="126"/>
+      <c r="I71" s="126"/>
+      <c r="J71" s="126"/>
+      <c r="K71" s="126"/>
+      <c r="L71" s="126"/>
+    </row>
+    <row r="72" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D72" s="115"/>
+      <c r="E72" s="115"/>
+      <c r="H72" s="177"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="120"/>
-      <c r="E72" s="121"/>
-    </row>
-    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="190"/>
-      <c r="B73" s="191"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="131"/>
-      <c r="E73" s="107"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="190"/>
-      <c r="B74" s="191"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="119"/>
+      <c r="E73" s="120"/>
+    </row>
+    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="189"/>
+      <c r="B74" s="190"/>
       <c r="C74" s="5"/>
-      <c r="D74" s="109"/>
-      <c r="E74" s="107"/>
-    </row>
-    <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="186"/>
-      <c r="B75" s="187"/>
+      <c r="D74" s="130"/>
+      <c r="E74" s="106"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="189"/>
+      <c r="B75" s="190"/>
       <c r="C75" s="5"/>
-      <c r="D75" s="109"/>
-      <c r="E75" s="107"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="108"/>
-      <c r="B76" s="110"/>
+      <c r="D75" s="108"/>
+      <c r="E75" s="106"/>
+    </row>
+    <row r="76" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="191"/>
+      <c r="B76" s="192"/>
       <c r="C76" s="5"/>
-      <c r="D76" s="109"/>
-      <c r="E76" s="107"/>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" s="51"/>
-      <c r="B77" s="50"/>
-      <c r="C77" s="50"/>
-      <c r="D77" s="60"/>
-      <c r="E77" s="60">
-        <f>SUM(D73:D76)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="31" t="s">
+      <c r="D76" s="108"/>
+      <c r="E76" s="106"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" s="107"/>
+      <c r="B77" s="109"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="108"/>
+      <c r="E77" s="106"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" s="51"/>
+      <c r="B78" s="50"/>
+      <c r="C78" s="50"/>
+      <c r="D78" s="60"/>
+      <c r="E78" s="60">
+        <f>SUM(D74:D77)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B80" s="31"/>
-      <c r="C80" s="31"/>
-      <c r="D80" s="32"/>
-      <c r="E80" s="104"/>
-    </row>
-    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="3" t="s">
+      <c r="B81" s="31"/>
+      <c r="C81" s="31"/>
+      <c r="D81" s="32"/>
+      <c r="E81" s="103"/>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B82" s="10"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="70">
-        <f>E77+E80</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="102" t="s">
+      <c r="B83" s="10"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="70">
+        <f>E78+E81</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="B84" s="103">
-        <f>E69</f>
-        <v>4429146.1900000004</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="102" t="s">
+      <c r="B85" s="102">
+        <f>E70</f>
+        <v>3770619.5600000005</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="B85" s="103">
-        <f>E69-E67</f>
-        <v>4429146.1900000004</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="102" t="s">
+      <c r="B86" s="102">
+        <f>E70-E68</f>
+        <v>3770619.5600000005</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="B86" s="103">
-        <f>E82-E80</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="102" t="s">
+      <c r="B87" s="102">
+        <f>E83-E81</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="101" t="s">
         <v>41</v>
       </c>
-      <c r="B87" s="103">
-        <f>E82</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="194"/>
-      <c r="B90" s="194"/>
-      <c r="C90" s="194"/>
-      <c r="D90" s="194"/>
-      <c r="E90" s="194"/>
-    </row>
-    <row r="91" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="194"/>
-      <c r="B91" s="194"/>
-      <c r="C91" s="194"/>
-      <c r="D91" s="194"/>
-      <c r="E91" s="194"/>
-    </row>
-    <row r="92" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="194"/>
-      <c r="B92" s="194"/>
-      <c r="C92" s="194"/>
-      <c r="D92" s="194"/>
-      <c r="E92" s="194"/>
-    </row>
-    <row r="94" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="23" t="s">
+      <c r="B88" s="102">
+        <f>E83</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="187"/>
+      <c r="B91" s="187"/>
+      <c r="C91" s="187"/>
+      <c r="D91" s="187"/>
+      <c r="E91" s="187"/>
+    </row>
+    <row r="92" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="187"/>
+      <c r="B92" s="187"/>
+      <c r="C92" s="187"/>
+      <c r="D92" s="187"/>
+      <c r="E92" s="187"/>
+    </row>
+    <row r="93" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="187"/>
+      <c r="B93" s="187"/>
+      <c r="C93" s="187"/>
+      <c r="D93" s="187"/>
+      <c r="E93" s="187"/>
+    </row>
+    <row r="95" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B94" s="128"/>
-      <c r="C94" s="24"/>
-    </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="34"/>
-      <c r="B95" s="61">
-        <v>0</v>
-      </c>
-      <c r="C95" s="26"/>
-    </row>
-    <row r="96" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="25" t="s">
+      <c r="B95" s="127"/>
+      <c r="C95" s="24"/>
+    </row>
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="34"/>
+      <c r="B96" s="61">
+        <v>0</v>
+      </c>
+      <c r="C96" s="26"/>
+    </row>
+    <row r="97" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B96" s="41">
+      <c r="B97" s="41">
         <f>PRORRATEO!F29</f>
-        <v>3500185.2800000003</v>
-      </c>
-      <c r="C96" s="24"/>
-    </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="25"/>
-      <c r="B97" s="41">
-        <v>0</v>
+        <v>3225298.1600000006</v>
       </c>
       <c r="C97" s="24"/>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="25" t="s">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="25"/>
+      <c r="B98" s="41">
+        <v>0</v>
+      </c>
+      <c r="C98" s="24"/>
+    </row>
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B98" s="111">
-        <f>B119</f>
-        <v>0</v>
-      </c>
-      <c r="C98" s="24"/>
-    </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="28"/>
-      <c r="B99" s="49"/>
+      <c r="B99" s="110">
+        <f>B120</f>
+        <v>0</v>
+      </c>
       <c r="C99" s="24"/>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="126" t="s">
-        <v>47</v>
-      </c>
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="28"/>
       <c r="B100" s="49"/>
       <c r="C100" s="24"/>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="40" t="s">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="125" t="s">
+        <v>47</v>
+      </c>
+      <c r="B101" s="49"/>
+      <c r="C101" s="24"/>
+    </row>
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B101" s="49">
-        <f>-B85</f>
-        <v>-4429146.1900000004</v>
-      </c>
-      <c r="C101" s="24"/>
-    </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="28" t="s">
+      <c r="B102" s="49">
+        <f>-B86</f>
+        <v>-3770619.5600000005</v>
+      </c>
+      <c r="C102" s="24"/>
+    </row>
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B102" s="49">
-        <f>-(B86)</f>
-        <v>0</v>
-      </c>
-      <c r="C102" s="24"/>
-    </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="33" t="s">
+      <c r="B103" s="49">
+        <f>-(B87)</f>
+        <v>0</v>
+      </c>
+      <c r="C103" s="24"/>
+    </row>
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B103" s="61">
-        <f>SUM(B95:B102)</f>
-        <v>-928960.91000000015</v>
-      </c>
-      <c r="C103" s="27"/>
-      <c r="D103" s="45"/>
-    </row>
-    <row r="104" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B104" s="42"/>
+      <c r="B104" s="61">
+        <f>SUM(B96:B103)</f>
+        <v>-545321.39999999991</v>
+      </c>
       <c r="C104" s="27"/>
       <c r="D104" s="45"/>
-      <c r="E104" s="129"/>
-      <c r="F104" s="130"/>
-    </row>
-    <row r="105" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="43"/>
+    </row>
+    <row r="105" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="42"/>
       <c r="C105" s="27"/>
-    </row>
-    <row r="106" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106"/>
-      <c r="B106" s="42"/>
-      <c r="C106" s="38"/>
-    </row>
-    <row r="107" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="134" t="s">
+      <c r="D105" s="45"/>
+      <c r="E105" s="128"/>
+      <c r="F105" s="129"/>
+    </row>
+    <row r="106" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="43"/>
+      <c r="C106" s="27"/>
+    </row>
+    <row r="107" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107"/>
+      <c r="B107" s="42"/>
+      <c r="C107" s="38"/>
+    </row>
+    <row r="108" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="133" t="s">
         <v>88</v>
       </c>
-      <c r="B107" s="135">
-        <v>-292661.08609999577</v>
-      </c>
-      <c r="C107" s="38"/>
-      <c r="D107" s="48"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="56" t="s">
+      <c r="B108" s="134">
+        <v>-864378.73609999567</v>
+      </c>
+      <c r="C108" s="38"/>
+      <c r="D108" s="48"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="B108" s="140">
-        <f>-B85</f>
-        <v>-4429146.1900000004</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="56" t="s">
+      <c r="B109" s="139">
+        <f>-B86</f>
+        <v>-3770619.5600000005</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="B109" s="140">
-        <f>-B86</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="56" t="s">
+      <c r="B110" s="139">
+        <f>-B87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="B110" s="140">
-        <f>B119</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="56" t="s">
+      <c r="B111" s="139">
+        <f>B120</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="B111" s="141">
+      <c r="B112" s="140">
         <f>PRORRATEO!F29</f>
-        <v>3500185.2800000003</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="138" t="s">
+        <v>3225298.1600000006</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="137" t="s">
         <v>49</v>
       </c>
-      <c r="B112" s="139">
-        <f>SUM(B107:C111)</f>
-        <v>-1221621.9960999964</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A113" s="136"/>
-      <c r="B113" s="136"/>
-    </row>
-    <row r="114" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A115" s="195" t="s">
+      <c r="B113" s="138">
+        <f>SUM(B108:C112)</f>
+        <v>-1409700.1360999956</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="135"/>
+      <c r="B114" s="135"/>
+    </row>
+    <row r="115" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="188" t="s">
         <v>33</v>
       </c>
-      <c r="B115" s="195"/>
-      <c r="C115" s="195"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A116" s="195"/>
-      <c r="B116" s="195"/>
-      <c r="C116" s="195"/>
-    </row>
-    <row r="117" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="123"/>
-      <c r="B117" s="37"/>
-      <c r="C117" s="37">
+      <c r="B116" s="188"/>
+      <c r="C116" s="188"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="188"/>
+      <c r="B117" s="188"/>
+      <c r="C117" s="188"/>
+    </row>
+    <row r="118" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="122"/>
+      <c r="B118" s="37"/>
+      <c r="C118" s="37">
         <v>40000</v>
       </c>
-      <c r="E117" s="142"/>
-    </row>
-    <row r="118" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="123"/>
-      <c r="B118" s="125"/>
-      <c r="C118" s="122"/>
-      <c r="D118" s="142"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="46" t="s">
+      <c r="E118" s="141"/>
+    </row>
+    <row r="119" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="122"/>
+      <c r="B119" s="124"/>
+      <c r="C119" s="121"/>
+      <c r="D119" s="141"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B119" s="124">
-        <f>SUM(B117:B118)</f>
-        <v>0</v>
-      </c>
-      <c r="C119" s="47"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M120" s="8"/>
-    </row>
-    <row r="121" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="194"/>
-      <c r="B121" s="194"/>
-      <c r="C121" s="194"/>
-      <c r="D121" s="194"/>
-      <c r="E121" s="194"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A122" s="194"/>
-      <c r="B122" s="194"/>
-      <c r="C122" s="194"/>
-      <c r="D122" s="194"/>
-      <c r="E122" s="194"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A123" s="194"/>
-      <c r="B123" s="194"/>
-      <c r="C123" s="194"/>
-      <c r="D123" s="194"/>
-      <c r="E123" s="194"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124" s="194"/>
-      <c r="B124" s="194"/>
-      <c r="C124" s="194"/>
-      <c r="D124" s="194"/>
-      <c r="E124" s="194"/>
+      <c r="B120" s="123">
+        <f>SUM(B118:B119)</f>
+        <v>0</v>
+      </c>
+      <c r="C120" s="47"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M121" s="8"/>
+    </row>
+    <row r="122" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="187"/>
+      <c r="B122" s="187"/>
+      <c r="C122" s="187"/>
+      <c r="D122" s="187"/>
+      <c r="E122" s="187"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" s="187"/>
+      <c r="B123" s="187"/>
+      <c r="C123" s="187"/>
+      <c r="D123" s="187"/>
+      <c r="E123" s="187"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" s="187"/>
+      <c r="B124" s="187"/>
+      <c r="C124" s="187"/>
+      <c r="D124" s="187"/>
+      <c r="E124" s="187"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" s="187"/>
+      <c r="B125" s="187"/>
+      <c r="C125" s="187"/>
+      <c r="D125" s="187"/>
+      <c r="E125" s="187"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A121:E124"/>
-    <mergeCell ref="A115:C116"/>
-    <mergeCell ref="A90:E92"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A34:B34"/>
+  <mergeCells count="16">
+    <mergeCell ref="A35:B35"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A122:E125"/>
+    <mergeCell ref="A116:C117"/>
+    <mergeCell ref="A91:E93"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2881,44 +2902,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="0.109375" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.28515625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="0.140625" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
     <col min="13" max="13" width="12" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="0.109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="0.140625" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="196"/>
-      <c r="E1" s="196"/>
-      <c r="F1" s="196"/>
-      <c r="G1" s="196"/>
-      <c r="H1" s="196"/>
-      <c r="I1" s="196"/>
-      <c r="J1" s="196"/>
-      <c r="K1" s="196"/>
-      <c r="L1" s="196"/>
+      <c r="D1" s="202"/>
+      <c r="E1" s="202"/>
+      <c r="F1" s="202"/>
+      <c r="G1" s="202"/>
+      <c r="H1" s="202"/>
+      <c r="I1" s="202"/>
+      <c r="J1" s="202"/>
+      <c r="K1" s="202"/>
+      <c r="L1" s="202"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2926,7 +2947,7 @@
         <v>85</v>
       </c>
       <c r="E2" s="6"/>
-      <c r="F2" s="166">
+      <c r="F2" s="165">
         <v>86134.56</v>
       </c>
       <c r="G2" s="6"/>
@@ -2936,14 +2957,14 @@
         <v>84</v>
       </c>
       <c r="K2" s="6"/>
-      <c r="L2" s="133">
-        <v>3774269.1700000004</v>
+      <c r="L2" s="132">
+        <v>3774269.17</v>
       </c>
       <c r="M2" s="57"/>
       <c r="N2" s="57"/>
       <c r="O2" s="22"/>
     </row>
-    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -2959,71 +2980,73 @@
       <c r="M3" s="58"/>
       <c r="N3" s="62"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="201" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="199" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="201" t="s">
+      <c r="B4" s="199" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="201" t="s">
+      <c r="C4" s="199" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="201" t="s">
+      <c r="D4" s="199" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="203" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="201" t="s">
+      <c r="F4" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="203" t="s">
+      <c r="G4" s="207" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="197" t="s">
+      <c r="H4" s="203" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="197" t="s">
+      <c r="I4" s="203" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="197" t="s">
+      <c r="J4" s="203" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="206" t="s">
+      <c r="K4" s="210" t="s">
         <v>83</v>
       </c>
       <c r="L4" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="199" t="s">
+      <c r="M4" s="205" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="208" t="s">
+      <c r="N4" s="197" t="s">
         <v>37</v>
       </c>
-      <c r="Q4" s="45"/>
-    </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="202"/>
-      <c r="B5" s="202"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="202"/>
-      <c r="E5" s="198"/>
-      <c r="F5" s="202"/>
-      <c r="G5" s="204"/>
-      <c r="H5" s="198"/>
-      <c r="I5" s="205"/>
-      <c r="J5" s="198"/>
-      <c r="K5" s="207"/>
+      <c r="Q4" s="132">
+        <v>3774269.17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="201"/>
+      <c r="B5" s="201"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="201"/>
+      <c r="E5" s="204"/>
+      <c r="F5" s="201"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="204"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="204"/>
+      <c r="K5" s="211"/>
       <c r="L5" s="63" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/02</v>
       </c>
-      <c r="M5" s="200"/>
-      <c r="N5" s="209"/>
-    </row>
-    <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="206"/>
+      <c r="N5" s="198"/>
+    </row>
+    <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="66">
         <v>1</v>
       </c>
@@ -3037,38 +3060,38 @@
       <c r="E6" s="76">
         <v>258261.01</v>
       </c>
-      <c r="F6" s="78">
+      <c r="F6" s="77">
         <f>E6</f>
         <v>258261.01</v>
       </c>
-      <c r="G6" s="79">
+      <c r="G6" s="78">
         <f t="shared" ref="G6:G23" si="0">E6-F6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="79">
+      <c r="H6" s="78">
         <f>IF(G6&gt;0,G6*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="80">
-        <v>0</v>
-      </c>
-      <c r="J6" s="81">
+      <c r="I6" s="79">
+        <v>0</v>
+      </c>
+      <c r="J6" s="80">
         <f>L$2*D6/100</f>
         <v>252498.60747300004</v>
       </c>
-      <c r="K6" s="167">
+      <c r="K6" s="166">
         <f t="shared" ref="K6:K23" si="1">F$2*D6/100</f>
         <v>5762.4020639999999</v>
       </c>
-      <c r="L6" s="83">
+      <c r="L6" s="82">
         <f>ROUND(SUM(G6:K6),0) + O6</f>
         <v>258261.01</v>
       </c>
-      <c r="M6" s="84">
+      <c r="M6" s="83">
         <f>ROUND(L6*6% + L6,0) + O6</f>
         <v>273757.01</v>
       </c>
-      <c r="N6" s="85">
+      <c r="N6" s="84">
         <f>ROUND(L6*3%,0) + L6</f>
         <v>266009.01</v>
       </c>
@@ -3076,7 +3099,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="66">
         <f>A6+1</f>
         <v>2</v>
@@ -3089,39 +3112,42 @@
         <v>5.88</v>
       </c>
       <c r="E7" s="76">
-        <v>747046.02</v>
-      </c>
-      <c r="F7" s="78"/>
-      <c r="G7" s="79">
+        <v>996449.02</v>
+      </c>
+      <c r="F7" s="77">
+        <f>200000+100000</f>
+        <v>300000</v>
+      </c>
+      <c r="G7" s="78">
         <f t="shared" si="0"/>
-        <v>747046.02</v>
-      </c>
-      <c r="H7" s="79">
+        <v>696449.02</v>
+      </c>
+      <c r="H7" s="78">
         <f t="shared" ref="H7:H23" si="2">IF(G7&gt;0,G7*3%,0)</f>
-        <v>22411.3806</v>
-      </c>
-      <c r="I7" s="80">
-        <v>0</v>
-      </c>
-      <c r="J7" s="81">
+        <v>20893.470600000001</v>
+      </c>
+      <c r="I7" s="79">
+        <v>0</v>
+      </c>
+      <c r="J7" s="80">
         <f t="shared" ref="J7:J23" si="3">L$2*D7%</f>
-        <v>221927.02719600001</v>
-      </c>
-      <c r="K7" s="167">
+        <v>221927.02719599998</v>
+      </c>
+      <c r="K7" s="166">
         <f t="shared" si="1"/>
         <v>5064.7121280000001</v>
       </c>
-      <c r="L7" s="83">
+      <c r="L7" s="82">
         <f t="shared" ref="L7:L23" si="4">ROUND(SUM(G7:K7),0) + O7</f>
-        <v>996449.02</v>
-      </c>
-      <c r="M7" s="84">
+        <v>944334.02</v>
+      </c>
+      <c r="M7" s="83">
         <f t="shared" ref="M7:M23" si="5">ROUND(L7*6% + L7,0) + O7</f>
-        <v>1056236.02</v>
-      </c>
-      <c r="N7" s="85">
+        <v>1000994.02</v>
+      </c>
+      <c r="N7" s="84">
         <f t="shared" ref="N7:N23" si="6">ROUND(L7*3%,0) + L7</f>
-        <v>1026342.02</v>
+        <v>972664.02</v>
       </c>
       <c r="O7" s="45">
         <f>O6+0.01</f>
@@ -3129,7 +3155,7 @@
       </c>
       <c r="P7" s="45"/>
     </row>
-    <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="66">
         <f t="shared" ref="A8:A23" si="7">A7+1</f>
         <v>3</v>
@@ -3142,46 +3168,48 @@
         <v>6.65</v>
       </c>
       <c r="E8" s="76">
-        <v>256717.03</v>
-      </c>
-      <c r="F8" s="78"/>
-      <c r="G8" s="79">
+        <v>536769.03</v>
+      </c>
+      <c r="F8" s="77">
+        <v>150000.03</v>
+      </c>
+      <c r="G8" s="78">
         <f t="shared" si="0"/>
-        <v>256717.03</v>
-      </c>
-      <c r="H8" s="79">
+        <v>386769</v>
+      </c>
+      <c r="H8" s="78">
         <f t="shared" si="2"/>
-        <v>7701.5108999999993</v>
-      </c>
-      <c r="I8" s="80">
-        <v>0</v>
-      </c>
-      <c r="J8" s="81">
+        <v>11603.07</v>
+      </c>
+      <c r="I8" s="79">
+        <v>0</v>
+      </c>
+      <c r="J8" s="80">
         <f t="shared" si="3"/>
-        <v>250988.89980500005</v>
-      </c>
-      <c r="K8" s="167">
+        <v>250988.89980500002</v>
+      </c>
+      <c r="K8" s="166">
         <f t="shared" si="1"/>
         <v>5727.9482400000006</v>
       </c>
-      <c r="L8" s="83">
+      <c r="L8" s="82">
         <f t="shared" si="4"/>
-        <v>521135.03</v>
-      </c>
-      <c r="M8" s="84">
+        <v>655089.03</v>
+      </c>
+      <c r="M8" s="83">
         <f t="shared" si="5"/>
-        <v>552403.03</v>
-      </c>
-      <c r="N8" s="85">
+        <v>694394.03</v>
+      </c>
+      <c r="N8" s="84">
         <f t="shared" si="6"/>
-        <v>536769.03</v>
+        <v>674742.03</v>
       </c>
       <c r="O8" s="45">
         <f t="shared" ref="O8:O24" si="8">O7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="66">
         <f t="shared" si="7"/>
         <v>4</v>
@@ -3194,40 +3222,40 @@
         <v>6.73</v>
       </c>
       <c r="E9" s="76">
-        <v>267599.03999999998</v>
-      </c>
-      <c r="F9" s="78">
+        <v>259805.04</v>
+      </c>
+      <c r="F9" s="77">
         <f t="shared" ref="F9:F23" si="9">E9</f>
-        <v>267599.03999999998</v>
-      </c>
-      <c r="G9" s="79">
+        <v>259805.04</v>
+      </c>
+      <c r="G9" s="78">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="79">
+      <c r="H9" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I9" s="80">
-        <v>0</v>
-      </c>
-      <c r="J9" s="81">
+      <c r="I9" s="79">
+        <v>0</v>
+      </c>
+      <c r="J9" s="80">
         <f t="shared" si="3"/>
-        <v>254008.31514100003</v>
-      </c>
-      <c r="K9" s="167">
+        <v>254008.315141</v>
+      </c>
+      <c r="K9" s="166">
         <f t="shared" si="1"/>
         <v>5796.855888</v>
       </c>
-      <c r="L9" s="83">
+      <c r="L9" s="82">
         <f t="shared" si="4"/>
         <v>259805.04</v>
       </c>
-      <c r="M9" s="84">
+      <c r="M9" s="83">
         <f t="shared" si="5"/>
         <v>275393.03999999998</v>
       </c>
-      <c r="N9" s="85">
+      <c r="N9" s="84">
         <f t="shared" si="6"/>
         <v>267599.04000000004</v>
       </c>
@@ -3237,7 +3265,7 @@
       </c>
       <c r="Q9" s="45"/>
     </row>
-    <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="66">
         <f t="shared" si="7"/>
         <v>5</v>
@@ -3250,42 +3278,39 @@
         <v>8.0399999999999991</v>
       </c>
       <c r="E10" s="76">
-        <v>647933.05000000005</v>
-      </c>
-      <c r="F10" s="78">
-        <f>E10</f>
-        <v>647933.05000000005</v>
-      </c>
-      <c r="G10" s="79">
+        <v>310376.05</v>
+      </c>
+      <c r="F10" s="77"/>
+      <c r="G10" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="79">
+        <v>310376.05</v>
+      </c>
+      <c r="H10" s="78">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="80">
-        <v>0</v>
-      </c>
-      <c r="J10" s="81">
+        <v>9311.2814999999991</v>
+      </c>
+      <c r="I10" s="79">
+        <v>0</v>
+      </c>
+      <c r="J10" s="80">
         <f t="shared" si="3"/>
-        <v>303451.24126799998</v>
-      </c>
-      <c r="K10" s="167">
+        <v>303451.24126799993</v>
+      </c>
+      <c r="K10" s="166">
         <f t="shared" si="1"/>
         <v>6925.2186239999983</v>
       </c>
-      <c r="L10" s="83">
+      <c r="L10" s="82">
         <f t="shared" si="4"/>
-        <v>310376.05</v>
-      </c>
-      <c r="M10" s="84">
+        <v>630064.05000000005</v>
+      </c>
+      <c r="M10" s="83">
         <f t="shared" si="5"/>
-        <v>328999.05</v>
-      </c>
-      <c r="N10" s="85">
+        <v>667868.05000000005</v>
+      </c>
+      <c r="N10" s="84">
         <f t="shared" si="6"/>
-        <v>319687.05</v>
+        <v>648966.05000000005</v>
       </c>
       <c r="O10" s="45">
         <f t="shared" si="8"/>
@@ -3293,7 +3318,7 @@
       </c>
       <c r="Q10" s="45"/>
     </row>
-    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="66">
         <f t="shared" si="7"/>
         <v>6</v>
@@ -3308,38 +3333,38 @@
       <c r="E11" s="76">
         <v>182597.06</v>
       </c>
-      <c r="F11" s="78">
+      <c r="F11" s="77">
         <f t="shared" si="9"/>
         <v>182597.06</v>
       </c>
-      <c r="G11" s="79">
+      <c r="G11" s="78">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="79">
+      <c r="H11" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I11" s="80">
-        <v>0</v>
-      </c>
-      <c r="J11" s="81">
+      <c r="I11" s="79">
+        <v>0</v>
+      </c>
+      <c r="J11" s="80">
         <f t="shared" si="3"/>
-        <v>178522.93174100004</v>
-      </c>
-      <c r="K11" s="167">
+        <v>178522.93174100001</v>
+      </c>
+      <c r="K11" s="166">
         <f t="shared" si="1"/>
         <v>4074.1646880000003</v>
       </c>
-      <c r="L11" s="83">
+      <c r="L11" s="82">
         <f t="shared" si="4"/>
         <v>182597.06</v>
       </c>
-      <c r="M11" s="84">
+      <c r="M11" s="83">
         <f t="shared" si="5"/>
         <v>193553.06</v>
       </c>
-      <c r="N11" s="85">
+      <c r="N11" s="84">
         <f t="shared" si="6"/>
         <v>188075.06</v>
       </c>
@@ -3348,7 +3373,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="66">
         <f t="shared" si="7"/>
         <v>7</v>
@@ -3361,46 +3386,46 @@
         <v>5.67</v>
       </c>
       <c r="E12" s="76">
-        <v>218885.07</v>
-      </c>
-      <c r="F12" s="78"/>
-      <c r="G12" s="79">
+        <v>444337.07</v>
+      </c>
+      <c r="F12" s="77"/>
+      <c r="G12" s="78">
         <f t="shared" si="0"/>
-        <v>218885.07</v>
-      </c>
-      <c r="H12" s="79">
+        <v>444337.07</v>
+      </c>
+      <c r="H12" s="78">
         <f t="shared" si="2"/>
-        <v>6566.5520999999999</v>
-      </c>
-      <c r="I12" s="80">
-        <v>0</v>
-      </c>
-      <c r="J12" s="81">
+        <v>13330.1121</v>
+      </c>
+      <c r="I12" s="79">
+        <v>0</v>
+      </c>
+      <c r="J12" s="80">
         <f t="shared" si="3"/>
-        <v>214001.06193900004</v>
-      </c>
-      <c r="K12" s="167">
+        <v>214001.06193900001</v>
+      </c>
+      <c r="K12" s="166">
         <f t="shared" si="1"/>
         <v>4883.8295519999992</v>
       </c>
-      <c r="L12" s="83">
+      <c r="L12" s="82">
         <f t="shared" si="4"/>
-        <v>444337.07</v>
-      </c>
-      <c r="M12" s="84">
+        <v>676552.07</v>
+      </c>
+      <c r="M12" s="83">
         <f t="shared" si="5"/>
-        <v>470997.07</v>
-      </c>
-      <c r="N12" s="85">
+        <v>717145.07</v>
+      </c>
+      <c r="N12" s="84">
         <f t="shared" si="6"/>
-        <v>457667.07</v>
+        <v>696849.07</v>
       </c>
       <c r="O12" s="45">
         <f t="shared" si="8"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="66">
         <f t="shared" si="7"/>
         <v>8</v>
@@ -3415,38 +3440,38 @@
       <c r="E13" s="76">
         <v>218885.08</v>
       </c>
-      <c r="F13" s="78">
+      <c r="F13" s="77">
         <f>E13</f>
         <v>218885.08</v>
       </c>
-      <c r="G13" s="79">
+      <c r="G13" s="78">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="79">
+      <c r="H13" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I13" s="80">
-        <v>0</v>
-      </c>
-      <c r="J13" s="81">
+      <c r="I13" s="79">
+        <v>0</v>
+      </c>
+      <c r="J13" s="80">
         <f t="shared" si="3"/>
-        <v>214001.06193900004</v>
-      </c>
-      <c r="K13" s="167">
+        <v>214001.06193900001</v>
+      </c>
+      <c r="K13" s="166">
         <f t="shared" si="1"/>
         <v>4883.8295519999992</v>
       </c>
-      <c r="L13" s="83">
+      <c r="L13" s="82">
         <f t="shared" si="4"/>
         <v>218885.08</v>
       </c>
-      <c r="M13" s="84">
+      <c r="M13" s="83">
         <f t="shared" si="5"/>
         <v>232018.08</v>
       </c>
-      <c r="N13" s="85">
+      <c r="N13" s="84">
         <f t="shared" si="6"/>
         <v>225452.08</v>
       </c>
@@ -3458,7 +3483,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="66">
         <f t="shared" si="7"/>
         <v>9</v>
@@ -3473,38 +3498,38 @@
       <c r="E14" s="76">
         <v>296093.09000000003</v>
       </c>
-      <c r="F14" s="78">
+      <c r="F14" s="77">
         <f t="shared" si="9"/>
         <v>296093.09000000003</v>
       </c>
-      <c r="G14" s="79">
+      <c r="G14" s="78">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="79">
+      <c r="H14" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I14" s="80">
-        <v>0</v>
-      </c>
-      <c r="J14" s="81">
+      <c r="I14" s="79">
+        <v>0</v>
+      </c>
+      <c r="J14" s="80">
         <f t="shared" si="3"/>
         <v>289486.44533900003</v>
       </c>
-      <c r="K14" s="167">
+      <c r="K14" s="166">
         <f t="shared" si="1"/>
         <v>6606.5207519999994</v>
       </c>
-      <c r="L14" s="83">
+      <c r="L14" s="82">
         <f t="shared" si="4"/>
         <v>296093.09000000003</v>
       </c>
-      <c r="M14" s="84">
+      <c r="M14" s="83">
         <f t="shared" si="5"/>
         <v>313859.09000000003</v>
       </c>
-      <c r="N14" s="85">
+      <c r="N14" s="84">
         <f t="shared" si="6"/>
         <v>304976.09000000003</v>
       </c>
@@ -3513,7 +3538,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="66">
         <f t="shared" si="7"/>
         <v>10</v>
@@ -3526,49 +3551,49 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="E15" s="76">
-        <v>189160.1</v>
-      </c>
-      <c r="F15" s="78">
-        <f>E15+RESUMEN!D58</f>
-        <v>409160.1</v>
-      </c>
-      <c r="G15" s="79">
+        <v>-30839.9</v>
+      </c>
+      <c r="F15" s="77">
+        <f>RESUMEN!D58</f>
+        <v>340000</v>
+      </c>
+      <c r="G15" s="78">
         <f t="shared" si="0"/>
-        <v>-219999.99999999997</v>
-      </c>
-      <c r="H15" s="79">
+        <v>-370839.9</v>
+      </c>
+      <c r="H15" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I15" s="80">
-        <v>0</v>
-      </c>
-      <c r="J15" s="81">
+      <c r="I15" s="79">
+        <v>0</v>
+      </c>
+      <c r="J15" s="80">
         <f t="shared" si="3"/>
-        <v>184939.18933000002</v>
-      </c>
-      <c r="K15" s="167">
+        <v>184939.18932999999</v>
+      </c>
+      <c r="K15" s="166">
         <f t="shared" si="1"/>
         <v>4220.5934400000006</v>
       </c>
-      <c r="L15" s="83">
+      <c r="L15" s="82">
         <f t="shared" si="4"/>
-        <v>-30839.9</v>
-      </c>
-      <c r="M15" s="84">
+        <v>-181679.9</v>
+      </c>
+      <c r="M15" s="83">
         <f t="shared" si="5"/>
-        <v>-32689.9</v>
-      </c>
-      <c r="N15" s="85">
+        <v>-192580.9</v>
+      </c>
+      <c r="N15" s="84">
         <f t="shared" si="6"/>
-        <v>-31764.9</v>
+        <v>-187129.9</v>
       </c>
       <c r="O15" s="45">
         <f t="shared" si="8"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="66">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -3583,38 +3608,38 @@
       <c r="E16" s="76">
         <v>217341.11</v>
       </c>
-      <c r="F16" s="78">
+      <c r="F16" s="77">
         <f t="shared" si="9"/>
         <v>217341.11</v>
       </c>
-      <c r="G16" s="79">
+      <c r="G16" s="78">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="79">
+      <c r="H16" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I16" s="80">
-        <v>0</v>
-      </c>
-      <c r="J16" s="81">
+      <c r="I16" s="79">
+        <v>0</v>
+      </c>
+      <c r="J16" s="80">
         <f t="shared" si="3"/>
-        <v>212491.35427100002</v>
-      </c>
-      <c r="K16" s="167">
+        <v>212491.35427099999</v>
+      </c>
+      <c r="K16" s="166">
         <f t="shared" si="1"/>
         <v>4849.375728</v>
       </c>
-      <c r="L16" s="83">
+      <c r="L16" s="82">
         <f t="shared" si="4"/>
         <v>217341.11</v>
       </c>
-      <c r="M16" s="84">
+      <c r="M16" s="83">
         <f t="shared" si="5"/>
         <v>230382.11</v>
       </c>
-      <c r="N16" s="85">
+      <c r="N16" s="84">
         <f t="shared" si="6"/>
         <v>223861.11</v>
       </c>
@@ -3623,7 +3648,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="66">
         <f t="shared" si="7"/>
         <v>12</v>
@@ -3638,38 +3663,38 @@
       <c r="E17" s="76">
         <v>214252.12</v>
       </c>
-      <c r="F17" s="78">
+      <c r="F17" s="77">
         <f t="shared" si="9"/>
         <v>214252.12</v>
       </c>
-      <c r="G17" s="79">
+      <c r="G17" s="78">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="79">
+      <c r="H17" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I17" s="80">
-        <v>0</v>
-      </c>
-      <c r="J17" s="81">
+      <c r="I17" s="79">
+        <v>0</v>
+      </c>
+      <c r="J17" s="80">
         <f t="shared" si="3"/>
         <v>209471.93893500001</v>
       </c>
-      <c r="K17" s="167">
+      <c r="K17" s="166">
         <f t="shared" si="1"/>
         <v>4780.4680799999996</v>
       </c>
-      <c r="L17" s="83">
+      <c r="L17" s="82">
         <f t="shared" si="4"/>
         <v>214252.12</v>
       </c>
-      <c r="M17" s="84">
+      <c r="M17" s="83">
         <f t="shared" si="5"/>
         <v>227107.12</v>
       </c>
-      <c r="N17" s="85">
+      <c r="N17" s="84">
         <f t="shared" si="6"/>
         <v>220680.12</v>
       </c>
@@ -3678,7 +3703,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="66">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -3693,38 +3718,38 @@
       <c r="E18" s="76">
         <v>426961.13</v>
       </c>
-      <c r="F18" s="78">
+      <c r="F18" s="77">
         <f>E18</f>
         <v>426961.13</v>
       </c>
-      <c r="G18" s="79">
+      <c r="G18" s="78">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="79">
+      <c r="H18" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I18" s="80">
-        <v>0</v>
-      </c>
-      <c r="J18" s="81">
+      <c r="I18" s="79">
+        <v>0</v>
+      </c>
+      <c r="J18" s="80">
         <f t="shared" si="3"/>
-        <v>417434.17020200007</v>
-      </c>
-      <c r="K18" s="167">
+        <v>417434.17020200001</v>
+      </c>
+      <c r="K18" s="166">
         <f t="shared" si="1"/>
         <v>9526.4823360000009</v>
       </c>
-      <c r="L18" s="83">
+      <c r="L18" s="82">
         <f t="shared" si="4"/>
         <v>426961.13</v>
       </c>
-      <c r="M18" s="84">
+      <c r="M18" s="83">
         <f t="shared" si="5"/>
         <v>452579.13</v>
       </c>
-      <c r="N18" s="85">
+      <c r="N18" s="84">
         <f t="shared" si="6"/>
         <v>439770.13</v>
       </c>
@@ -3733,7 +3758,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="66">
         <f t="shared" si="7"/>
         <v>14</v>
@@ -3746,46 +3771,46 @@
         <v>3.3</v>
       </c>
       <c r="E19" s="76">
-        <v>577588.14</v>
-      </c>
-      <c r="F19" s="78"/>
-      <c r="G19" s="79">
+        <v>722309.14</v>
+      </c>
+      <c r="F19" s="77"/>
+      <c r="G19" s="78">
         <f t="shared" si="0"/>
-        <v>577588.14</v>
-      </c>
-      <c r="H19" s="79">
+        <v>722309.14</v>
+      </c>
+      <c r="H19" s="78">
         <f t="shared" si="2"/>
-        <v>17327.644199999999</v>
-      </c>
-      <c r="I19" s="80">
-        <v>0</v>
-      </c>
-      <c r="J19" s="81">
+        <v>21669.2742</v>
+      </c>
+      <c r="I19" s="79">
+        <v>0</v>
+      </c>
+      <c r="J19" s="80">
         <f t="shared" si="3"/>
-        <v>124550.88261000002</v>
-      </c>
-      <c r="K19" s="167">
+        <v>124550.88261</v>
+      </c>
+      <c r="K19" s="166">
         <f t="shared" si="1"/>
         <v>2842.4404799999993</v>
       </c>
-      <c r="L19" s="83">
+      <c r="L19" s="82">
         <f t="shared" si="4"/>
-        <v>722309.14</v>
-      </c>
-      <c r="M19" s="84">
+        <v>871372.14</v>
+      </c>
+      <c r="M19" s="83">
         <f t="shared" si="5"/>
-        <v>765648.14</v>
-      </c>
-      <c r="N19" s="85">
+        <v>923654.14</v>
+      </c>
+      <c r="N19" s="84">
         <f t="shared" si="6"/>
-        <v>743978.14</v>
+        <v>897513.14</v>
       </c>
       <c r="O19" s="45">
         <f t="shared" si="8"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="66">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -3798,48 +3823,49 @@
         <v>1.8</v>
       </c>
       <c r="E20" s="76">
-        <v>69487.149999999994</v>
-      </c>
-      <c r="F20" s="78">
+        <v>67402.149999999994</v>
+      </c>
+      <c r="F20" s="77">
+        <f>71572.15</f>
         <v>71572.149999999994</v>
       </c>
-      <c r="G20" s="79">
+      <c r="G20" s="78">
         <f t="shared" si="0"/>
-        <v>-2085</v>
-      </c>
-      <c r="H20" s="79">
+        <v>-4170</v>
+      </c>
+      <c r="H20" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I20" s="80">
-        <v>0</v>
-      </c>
-      <c r="J20" s="81">
+      <c r="I20" s="79">
+        <v>0</v>
+      </c>
+      <c r="J20" s="80">
         <f t="shared" si="3"/>
-        <v>67936.845060000021</v>
-      </c>
-      <c r="K20" s="167">
+        <v>67936.845060000007</v>
+      </c>
+      <c r="K20" s="166">
         <f t="shared" si="1"/>
         <v>1550.4220800000001</v>
       </c>
-      <c r="L20" s="83">
+      <c r="L20" s="82">
         <f t="shared" si="4"/>
-        <v>67402.149999999994</v>
-      </c>
-      <c r="M20" s="84">
+        <v>65317.15</v>
+      </c>
+      <c r="M20" s="83">
         <f t="shared" si="5"/>
-        <v>71446.149999999994</v>
-      </c>
-      <c r="N20" s="85">
+        <v>69236.149999999994</v>
+      </c>
+      <c r="N20" s="84">
         <f t="shared" si="6"/>
-        <v>69424.149999999994</v>
+        <v>67277.149999999994</v>
       </c>
       <c r="O20" s="45">
         <f t="shared" si="8"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="66">
         <f t="shared" si="7"/>
         <v>16</v>
@@ -3854,38 +3880,38 @@
       <c r="E21" s="76">
         <v>124305.16</v>
       </c>
-      <c r="F21" s="78">
+      <c r="F21" s="77">
         <f>E21</f>
         <v>124305.16</v>
       </c>
-      <c r="G21" s="79">
+      <c r="G21" s="78">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H21" s="79">
+      <c r="H21" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I21" s="80">
-        <v>0</v>
-      </c>
-      <c r="J21" s="81">
+      <c r="I21" s="79">
+        <v>0</v>
+      </c>
+      <c r="J21" s="80">
         <f t="shared" si="3"/>
-        <v>121531.46727400001</v>
-      </c>
-      <c r="K21" s="167">
+        <v>121531.467274</v>
+      </c>
+      <c r="K21" s="166">
         <f t="shared" si="1"/>
         <v>2773.5328319999999</v>
       </c>
-      <c r="L21" s="83">
+      <c r="L21" s="82">
         <f t="shared" si="4"/>
         <v>124305.16</v>
       </c>
-      <c r="M21" s="84">
+      <c r="M21" s="83">
         <f t="shared" si="5"/>
         <v>131763.16</v>
       </c>
-      <c r="N21" s="85">
+      <c r="N21" s="84">
         <f t="shared" si="6"/>
         <v>128034.16</v>
       </c>
@@ -3895,7 +3921,7 @@
       </c>
       <c r="Q21" s="44"/>
     </row>
-    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="66">
         <f t="shared" si="7"/>
         <v>17</v>
@@ -3908,48 +3934,48 @@
         <v>2.61</v>
       </c>
       <c r="E22" s="77">
-        <v>204536.17</v>
-      </c>
-      <c r="F22" s="78">
-        <v>0</v>
-      </c>
-      <c r="G22" s="79">
+        <v>311429.17</v>
+      </c>
+      <c r="F22" s="77">
+        <v>0</v>
+      </c>
+      <c r="G22" s="78">
         <f t="shared" si="0"/>
-        <v>204536.17</v>
-      </c>
-      <c r="H22" s="79">
+        <v>311429.17</v>
+      </c>
+      <c r="H22" s="78">
         <f t="shared" si="2"/>
-        <v>6136.0851000000002</v>
-      </c>
-      <c r="I22" s="80">
-        <v>0</v>
-      </c>
-      <c r="J22" s="81">
+        <v>9342.8750999999993</v>
+      </c>
+      <c r="I22" s="79">
+        <v>0</v>
+      </c>
+      <c r="J22" s="80">
         <f t="shared" si="3"/>
-        <v>98508.425337000008</v>
-      </c>
-      <c r="K22" s="167">
+        <v>98508.425336999993</v>
+      </c>
+      <c r="K22" s="166">
         <f t="shared" si="1"/>
         <v>2248.1120159999996</v>
       </c>
-      <c r="L22" s="83">
+      <c r="L22" s="82">
         <f t="shared" si="4"/>
-        <v>311429.17</v>
-      </c>
-      <c r="M22" s="84">
+        <v>421529.17</v>
+      </c>
+      <c r="M22" s="83">
         <f t="shared" si="5"/>
-        <v>330115.17</v>
-      </c>
-      <c r="N22" s="85">
+        <v>446821.17</v>
+      </c>
+      <c r="N22" s="84">
         <f t="shared" si="6"/>
-        <v>320772.17</v>
+        <v>434175.17</v>
       </c>
       <c r="O22" s="45">
         <f t="shared" si="8"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="66">
         <f t="shared" si="7"/>
         <v>18</v>
@@ -3957,45 +3983,45 @@
       <c r="B23" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="132"/>
+      <c r="C23" s="131"/>
       <c r="D23" s="75">
         <v>4.28</v>
       </c>
       <c r="E23" s="76">
         <v>165225.18</v>
       </c>
-      <c r="F23" s="78">
+      <c r="F23" s="77">
         <f t="shared" si="9"/>
         <v>165225.18</v>
       </c>
-      <c r="G23" s="79">
+      <c r="G23" s="78">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H23" s="79">
+      <c r="H23" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I23" s="80">
-        <v>0</v>
-      </c>
-      <c r="J23" s="81">
+      <c r="I23" s="79">
+        <v>0</v>
+      </c>
+      <c r="J23" s="80">
         <f t="shared" si="3"/>
-        <v>161538.72047600005</v>
-      </c>
-      <c r="K23" s="167">
+        <v>161538.72047600002</v>
+      </c>
+      <c r="K23" s="166">
         <f t="shared" si="1"/>
         <v>3686.5591680000002</v>
       </c>
-      <c r="L23" s="83">
+      <c r="L23" s="82">
         <f t="shared" si="4"/>
         <v>165225.18</v>
       </c>
-      <c r="M23" s="84">
+      <c r="M23" s="83">
         <f t="shared" si="5"/>
         <v>175139.18</v>
       </c>
-      <c r="N23" s="85">
+      <c r="N23" s="84">
         <f t="shared" si="6"/>
         <v>170182.18</v>
       </c>
@@ -4004,237 +4030,231 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="66"/>
       <c r="B24" s="66"/>
       <c r="C24" s="67"/>
       <c r="D24" s="75"/>
       <c r="E24" s="76"/>
-      <c r="F24" s="156"/>
-      <c r="G24" s="79"/>
-      <c r="H24" s="79"/>
-      <c r="I24" s="80"/>
-      <c r="J24" s="81"/>
-      <c r="K24" s="82"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="84"/>
-      <c r="N24" s="85"/>
+      <c r="F24" s="155"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="78"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="80"/>
+      <c r="K24" s="81"/>
+      <c r="L24" s="82"/>
+      <c r="M24" s="83"/>
+      <c r="N24" s="84"/>
       <c r="O24" s="45">
         <f t="shared" si="8"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="86"/>
+    <row r="25" spans="1:17" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="85"/>
       <c r="B25" s="66"/>
       <c r="C25" s="67"/>
       <c r="D25" s="75"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="89"/>
-      <c r="G25" s="90"/>
-      <c r="H25" s="79"/>
-      <c r="I25" s="80"/>
-      <c r="J25" s="91"/>
-      <c r="K25" s="92"/>
-      <c r="L25" s="83"/>
-      <c r="M25" s="84"/>
-      <c r="N25" s="85"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="89"/>
+      <c r="H25" s="78"/>
+      <c r="I25" s="79"/>
+      <c r="J25" s="90"/>
+      <c r="K25" s="91"/>
+      <c r="L25" s="82"/>
+      <c r="M25" s="83"/>
+      <c r="N25" s="84"/>
       <c r="O25" s="45"/>
     </row>
-    <row r="26" spans="1:17" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="86"/>
+    <row r="26" spans="1:17" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="85"/>
       <c r="B26" s="68"/>
       <c r="C26" s="67"/>
       <c r="D26" s="75"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="89"/>
-      <c r="G26" s="90"/>
-      <c r="H26" s="79"/>
-      <c r="I26" s="80"/>
-      <c r="J26" s="91"/>
-      <c r="K26" s="92"/>
-      <c r="L26" s="83"/>
-      <c r="M26" s="84"/>
-      <c r="N26" s="85"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="88"/>
+      <c r="G26" s="89"/>
+      <c r="H26" s="78"/>
+      <c r="I26" s="79"/>
+      <c r="J26" s="90"/>
+      <c r="K26" s="91"/>
+      <c r="L26" s="82"/>
+      <c r="M26" s="83"/>
+      <c r="N26" s="84"/>
       <c r="O26" s="45"/>
     </row>
-    <row r="27" spans="1:17" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="87"/>
+    <row r="27" spans="1:17" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="86"/>
       <c r="B27" s="66"/>
       <c r="C27" s="67"/>
       <c r="D27" s="75"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="89"/>
-      <c r="G27" s="90"/>
-      <c r="H27" s="79"/>
-      <c r="I27" s="80"/>
-      <c r="J27" s="91"/>
-      <c r="K27" s="92"/>
-      <c r="L27" s="83"/>
-      <c r="M27" s="84"/>
-      <c r="N27" s="85"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="78"/>
+      <c r="I27" s="79"/>
+      <c r="J27" s="90"/>
+      <c r="K27" s="91"/>
+      <c r="L27" s="82"/>
+      <c r="M27" s="83"/>
+      <c r="N27" s="84"/>
       <c r="O27" s="45"/>
     </row>
-    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="66"/>
-      <c r="B28" s="93"/>
-      <c r="C28" s="93"/>
+      <c r="B28" s="92"/>
+      <c r="C28" s="92"/>
       <c r="D28" s="75"/>
-      <c r="E28" s="88"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="90"/>
-      <c r="H28" s="79"/>
-      <c r="I28" s="80"/>
-      <c r="J28" s="91"/>
-      <c r="K28" s="92"/>
-      <c r="L28" s="94"/>
-      <c r="M28" s="95"/>
-      <c r="N28" s="96"/>
+      <c r="E28" s="87"/>
+      <c r="F28" s="88"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="78"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="90"/>
+      <c r="K28" s="91"/>
+      <c r="L28" s="93"/>
+      <c r="M28" s="94"/>
+      <c r="N28" s="95"/>
       <c r="O28" s="45"/>
     </row>
-    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="97"/>
-      <c r="B29" s="98"/>
-      <c r="C29" s="98"/>
-      <c r="D29" s="99">
+    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="96"/>
+      <c r="B29" s="97"/>
+      <c r="C29" s="97"/>
+      <c r="D29" s="98">
         <f>SUM(D6:D28)</f>
         <v>100.08</v>
       </c>
       <c r="E29" s="55">
         <f>SUM(E6:E28)</f>
-        <v>5282872.71</v>
+        <v>5721957.71</v>
       </c>
       <c r="F29" s="64">
         <f>SUM(F6:F28)</f>
-        <v>3500185.2800000003</v>
+        <v>3225298.1600000006</v>
       </c>
       <c r="G29" s="64">
         <f>SUM(G6:G28)</f>
-        <v>1782687.4300000002</v>
+        <v>2496659.5500000003</v>
       </c>
       <c r="H29" s="64">
         <f t="shared" ref="H29:M29" si="10">SUM(H6:H28)</f>
-        <v>60143.17289999999</v>
+        <v>86150.083500000008</v>
       </c>
       <c r="I29" s="64">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J29" s="137">
+      <c r="J29" s="136">
         <f t="shared" si="10"/>
-        <v>3777288.5853360011</v>
+        <v>3777288.5853359997</v>
       </c>
       <c r="K29" s="64">
         <f t="shared" si="10"/>
         <v>86203.467647999991</v>
       </c>
-      <c r="L29" s="100">
+      <c r="L29" s="99">
         <f>SUM(L6:L23)</f>
-        <v>5706323.71</v>
-      </c>
-      <c r="M29" s="100">
+        <v>6446303.71</v>
+      </c>
+      <c r="M29" s="99">
         <f t="shared" si="10"/>
-        <v>6048705.71</v>
-      </c>
-      <c r="N29" s="100">
+        <v>6833082.71</v>
+      </c>
+      <c r="N29" s="99">
         <f>SUM(N6:N28)</f>
-        <v>5877513.71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>6639695.71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="52"/>
       <c r="C30" s="52"/>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="194" t="str">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="187" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="194"/>
-      <c r="D32" s="194"/>
-      <c r="E32" s="194"/>
-      <c r="F32" s="194"/>
-      <c r="G32" s="194"/>
-      <c r="H32" s="194"/>
-      <c r="I32" s="194"/>
-      <c r="J32" s="194"/>
-      <c r="K32" s="194"/>
-      <c r="L32" s="194"/>
-    </row>
-    <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="194"/>
-      <c r="C33" s="194"/>
-      <c r="D33" s="194"/>
-      <c r="E33" s="194"/>
-      <c r="F33" s="194"/>
-      <c r="G33" s="194"/>
-      <c r="H33" s="194"/>
-      <c r="I33" s="194"/>
-      <c r="J33" s="194"/>
-      <c r="K33" s="194"/>
-      <c r="L33" s="194"/>
-    </row>
-    <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="194"/>
-      <c r="C34" s="194"/>
-      <c r="D34" s="194"/>
-      <c r="E34" s="194"/>
-      <c r="F34" s="194"/>
-      <c r="G34" s="194"/>
-      <c r="H34" s="194"/>
-      <c r="I34" s="194"/>
-      <c r="J34" s="194"/>
-      <c r="K34" s="194"/>
-      <c r="L34" s="194"/>
-    </row>
-    <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="194"/>
-      <c r="C35" s="194"/>
-      <c r="D35" s="194"/>
-      <c r="E35" s="194"/>
-      <c r="F35" s="194"/>
-      <c r="G35" s="194"/>
-      <c r="H35" s="194"/>
-      <c r="I35" s="194"/>
-      <c r="J35" s="194"/>
-      <c r="K35" s="194"/>
-      <c r="L35" s="194"/>
-    </row>
-    <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="194"/>
-      <c r="C36" s="194"/>
-      <c r="D36" s="194"/>
-      <c r="E36" s="194"/>
-      <c r="F36" s="194"/>
-      <c r="G36" s="194"/>
-      <c r="H36" s="194"/>
-      <c r="I36" s="194"/>
-      <c r="J36" s="194"/>
-      <c r="K36" s="194"/>
-      <c r="L36" s="194"/>
-    </row>
-    <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="194"/>
-      <c r="C37" s="194"/>
-      <c r="D37" s="194"/>
-      <c r="E37" s="194"/>
-      <c r="F37" s="194"/>
-      <c r="G37" s="194"/>
-      <c r="H37" s="194"/>
-      <c r="I37" s="194"/>
-      <c r="J37" s="194"/>
-      <c r="K37" s="194"/>
-      <c r="L37" s="194"/>
+      <c r="C32" s="187"/>
+      <c r="D32" s="187"/>
+      <c r="E32" s="187"/>
+      <c r="F32" s="187"/>
+      <c r="G32" s="187"/>
+      <c r="H32" s="187"/>
+      <c r="I32" s="187"/>
+      <c r="J32" s="187"/>
+      <c r="K32" s="187"/>
+      <c r="L32" s="187"/>
+    </row>
+    <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="187"/>
+      <c r="C33" s="187"/>
+      <c r="D33" s="187"/>
+      <c r="E33" s="187"/>
+      <c r="F33" s="187"/>
+      <c r="G33" s="187"/>
+      <c r="H33" s="187"/>
+      <c r="I33" s="187"/>
+      <c r="J33" s="187"/>
+      <c r="K33" s="187"/>
+      <c r="L33" s="187"/>
+    </row>
+    <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="187"/>
+      <c r="C34" s="187"/>
+      <c r="D34" s="187"/>
+      <c r="E34" s="187"/>
+      <c r="F34" s="187"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="187"/>
+      <c r="I34" s="187"/>
+      <c r="J34" s="187"/>
+      <c r="K34" s="187"/>
+      <c r="L34" s="187"/>
+    </row>
+    <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="187"/>
+      <c r="C35" s="187"/>
+      <c r="D35" s="187"/>
+      <c r="E35" s="187"/>
+      <c r="F35" s="187"/>
+      <c r="G35" s="187"/>
+      <c r="H35" s="187"/>
+      <c r="I35" s="187"/>
+      <c r="J35" s="187"/>
+      <c r="K35" s="187"/>
+      <c r="L35" s="187"/>
+    </row>
+    <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="187"/>
+      <c r="C36" s="187"/>
+      <c r="D36" s="187"/>
+      <c r="E36" s="187"/>
+      <c r="F36" s="187"/>
+      <c r="G36" s="187"/>
+      <c r="H36" s="187"/>
+      <c r="I36" s="187"/>
+      <c r="J36" s="187"/>
+      <c r="K36" s="187"/>
+      <c r="L36" s="187"/>
+    </row>
+    <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="187"/>
+      <c r="C37" s="187"/>
+      <c r="D37" s="187"/>
+      <c r="E37" s="187"/>
+      <c r="F37" s="187"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="187"/>
+      <c r="I37" s="187"/>
+      <c r="J37" s="187"/>
+      <c r="K37" s="187"/>
+      <c r="L37" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="B32:L37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="E4:E5"/>
@@ -4244,6 +4264,12 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="B32:L37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4253,10 +4279,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="C5:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C5" s="179" t="s">
+    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C5" s="178" t="s">
         <v>89</v>
       </c>
       <c r="E5" t="s">

--- a/2026/YRIGOYEN 7630/ENERO/YRIGOYEN7630-Enero.xlsx
+++ b/2026/YRIGOYEN 7630/ENERO/YRIGOYEN7630-Enero.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\YRIGOYEN 7630\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EC4CCF-1854-42D2-89D6-32CAEF3959DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF07C49-090D-4BDA-8BED-CAD99B8E128C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="116">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -197,9 +197,6 @@
 </t>
   </si>
   <si>
-    <t>CONSORCIO DE PROPIETARIOS DEL EDIFICIO CALLE YRIGOYEN 9730</t>
-  </si>
-  <si>
     <t>CUIT DEL EDIFICIO: 30-55421584-6</t>
   </si>
   <si>
@@ -296,12 +293,6 @@
     <t>SALDO EN BANCO</t>
   </si>
   <si>
-    <t>laurasmiet@gmail.com</t>
-  </si>
-  <si>
-    <t>AGREGAR A LA CADENA</t>
-  </si>
-  <si>
     <t>Gastos bancarios</t>
   </si>
   <si>
@@ -378,6 +369,12 @@
   </si>
   <si>
     <t>Abonado Sra. Ana Maria Castro</t>
+  </si>
+  <si>
+    <t>CONSORCIO DE PROPIETARIOS DEL EDIFICIO CALLE YRIGOYEN 7630</t>
+  </si>
+  <si>
+    <t>Le pusimos plata demas en enero 2026 a esta Sra.</t>
   </si>
 </sst>
 </file>
@@ -608,7 +605,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -675,6 +672,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -1088,7 +1091,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="212">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1333,7 +1336,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1352,35 +1354,71 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1388,45 +1426,19 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1827,12 +1839,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
-      <c r="B3" s="193" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" s="193"/>
-      <c r="D3" s="193"/>
-      <c r="E3" s="194"/>
+      <c r="B3" s="188" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="189"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
@@ -1847,10 +1859,10 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="73" t="s">
@@ -1860,7 +1872,7 @@
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
@@ -1870,49 +1882,49 @@
       <c r="E6" s="21"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="196" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="196"/>
+      <c r="B8" s="191" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="191"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="196"/>
-      <c r="C9" s="196"/>
+      <c r="B9" s="191"/>
+      <c r="C9" s="191"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="196"/>
-      <c r="C10" s="196"/>
+      <c r="B10" s="191"/>
+      <c r="C10" s="191"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="195" t="s">
+      <c r="A13" s="190" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="195"/>
-      <c r="C13" s="195"/>
-      <c r="D13" s="195"/>
-      <c r="E13" s="195"/>
+      <c r="B13" s="190"/>
+      <c r="C13" s="190"/>
+      <c r="D13" s="190"/>
+      <c r="E13" s="190"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="195"/>
-      <c r="B14" s="195"/>
-      <c r="C14" s="195"/>
-      <c r="D14" s="195"/>
-      <c r="E14" s="195"/>
+      <c r="A14" s="190"/>
+      <c r="B14" s="190"/>
+      <c r="C14" s="190"/>
+      <c r="D14" s="190"/>
+      <c r="E14" s="190"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="195"/>
-      <c r="B15" s="195"/>
-      <c r="C15" s="195"/>
-      <c r="D15" s="195"/>
-      <c r="E15" s="195"/>
+      <c r="A15" s="190"/>
+      <c r="B15" s="190"/>
+      <c r="C15" s="190"/>
+      <c r="D15" s="190"/>
+      <c r="E15" s="190"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="195"/>
-      <c r="B16" s="195"/>
-      <c r="C16" s="195"/>
-      <c r="D16" s="195"/>
-      <c r="E16" s="195"/>
+      <c r="A16" s="190"/>
+      <c r="B16" s="190"/>
+      <c r="C16" s="190"/>
+      <c r="D16" s="190"/>
+      <c r="E16" s="190"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -1939,7 +1951,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2042,10 +2054,10 @@
       <c r="E32" s="144"/>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="191" t="s">
-        <v>101</v>
-      </c>
-      <c r="B33" s="192"/>
+      <c r="A33" s="186" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="187"/>
       <c r="C33" s="54"/>
       <c r="D33" s="158">
         <v>35000</v>
@@ -2053,10 +2065,10 @@
       <c r="E33" s="145"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="179" t="s">
-        <v>105</v>
-      </c>
-      <c r="B34" s="180"/>
+      <c r="A34" s="178" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="179"/>
       <c r="C34" s="54"/>
       <c r="D34" s="158">
         <v>112000</v>
@@ -2064,17 +2076,17 @@
       <c r="E34" s="145"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="191" t="s">
-        <v>106</v>
-      </c>
-      <c r="B35" s="192"/>
+      <c r="A35" s="186" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="187"/>
       <c r="C35" s="54"/>
-      <c r="D35" s="182">
+      <c r="D35" s="181">
         <v>147300</v>
       </c>
       <c r="E35" s="145"/>
       <c r="H35" s="156" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2099,26 +2111,26 @@
       <c r="E37" s="147"/>
     </row>
     <row r="38" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="189" t="s">
-        <v>93</v>
-      </c>
-      <c r="B38" s="190"/>
+      <c r="A38" s="192" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="193"/>
       <c r="C38" s="56"/>
-      <c r="D38" s="183">
+      <c r="D38" s="182">
         <f>6696+26570</f>
         <v>33266</v>
       </c>
-      <c r="E38" s="181" t="s">
-        <v>107</v>
+      <c r="E38" s="180" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="191" t="s">
-        <v>94</v>
-      </c>
-      <c r="B39" s="192"/>
+      <c r="A39" s="186" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="187"/>
       <c r="C39" s="56"/>
-      <c r="D39" s="184">
+      <c r="D39" s="183">
         <v>54278</v>
       </c>
       <c r="E39" s="148" t="str">
@@ -2153,34 +2165,34 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="54"/>
-      <c r="D42" s="185">
+      <c r="D42" s="184">
         <v>937097.26</v>
       </c>
       <c r="E42" s="159" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G42" s="126"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="54"/>
-      <c r="D43" s="185">
+      <c r="D43" s="184">
         <v>10602.27</v>
       </c>
       <c r="E43" s="159" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="54"/>
-      <c r="D44" s="185">
+      <c r="D44" s="184">
         <v>75532.289999999994</v>
       </c>
       <c r="E44" s="159" t="str">
@@ -2195,7 +2207,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -2203,7 +2215,7 @@
         <v>132242.74</v>
       </c>
       <c r="E45" s="159" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -2259,7 +2271,7 @@
     </row>
     <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -2267,12 +2279,12 @@
         <v>81386.33</v>
       </c>
       <c r="E50" s="159" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B51" s="162"/>
       <c r="C51" s="5"/>
@@ -2280,12 +2292,12 @@
         <v>38806.65</v>
       </c>
       <c r="E51" s="159" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -2293,20 +2305,20 @@
         <v>26145.55</v>
       </c>
       <c r="E52" s="159" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="189" t="s">
-        <v>77</v>
-      </c>
-      <c r="B53" s="190"/>
+      <c r="A53" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="B53" s="193"/>
       <c r="C53" s="5"/>
       <c r="D53" s="162">
         <v>377536.65</v>
       </c>
       <c r="E53" s="159" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2330,7 +2342,7 @@
     </row>
     <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="164" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B56" s="157"/>
       <c r="C56" s="5"/>
@@ -2338,12 +2350,12 @@
         <v>85000</v>
       </c>
       <c r="E56" s="163" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="164" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B57" s="157"/>
       <c r="C57" s="5"/>
@@ -2351,25 +2363,25 @@
         <v>45000</v>
       </c>
       <c r="E57" s="163" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="164" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B58" s="157"/>
       <c r="C58" s="5"/>
       <c r="D58" s="108">
         <v>340000</v>
       </c>
-      <c r="E58" s="186" t="s">
-        <v>116</v>
+      <c r="E58" s="185" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="164" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B59" s="157"/>
       <c r="C59" s="5"/>
@@ -2377,33 +2389,33 @@
         <v>59600</v>
       </c>
       <c r="E59" s="163" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="189" t="s">
-        <v>114</v>
-      </c>
-      <c r="B60" s="190"/>
+      <c r="A60" s="192" t="s">
+        <v>111</v>
+      </c>
+      <c r="B60" s="193"/>
       <c r="C60" s="5"/>
       <c r="D60" s="108">
         <v>35500</v>
       </c>
       <c r="E60" s="163" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="189" t="s">
-        <v>111</v>
-      </c>
-      <c r="B61" s="190"/>
+      <c r="A61" s="192" t="s">
+        <v>108</v>
+      </c>
+      <c r="B61" s="193"/>
       <c r="C61" s="5"/>
       <c r="D61" s="108">
         <v>45000</v>
       </c>
       <c r="E61" s="163" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2429,7 +2441,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -2440,7 +2452,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -2526,22 +2538,22 @@
       <c r="E73" s="120"/>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="189"/>
-      <c r="B74" s="190"/>
+      <c r="A74" s="192"/>
+      <c r="B74" s="193"/>
       <c r="C74" s="5"/>
       <c r="D74" s="130"/>
       <c r="E74" s="106"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="189"/>
-      <c r="B75" s="190"/>
+      <c r="A75" s="192"/>
+      <c r="B75" s="193"/>
       <c r="C75" s="5"/>
       <c r="D75" s="108"/>
       <c r="E75" s="106"/>
     </row>
     <row r="76" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="191"/>
-      <c r="B76" s="192"/>
+      <c r="A76" s="186"/>
+      <c r="B76" s="187"/>
       <c r="C76" s="5"/>
       <c r="D76" s="108"/>
       <c r="E76" s="106"/>
@@ -2627,25 +2639,25 @@
     <row r="89" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="90" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="187"/>
-      <c r="B91" s="187"/>
-      <c r="C91" s="187"/>
-      <c r="D91" s="187"/>
-      <c r="E91" s="187"/>
+      <c r="A91" s="194"/>
+      <c r="B91" s="194"/>
+      <c r="C91" s="194"/>
+      <c r="D91" s="194"/>
+      <c r="E91" s="194"/>
     </row>
     <row r="92" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="187"/>
-      <c r="B92" s="187"/>
-      <c r="C92" s="187"/>
-      <c r="D92" s="187"/>
-      <c r="E92" s="187"/>
+      <c r="A92" s="194"/>
+      <c r="B92" s="194"/>
+      <c r="C92" s="194"/>
+      <c r="D92" s="194"/>
+      <c r="E92" s="194"/>
     </row>
     <row r="93" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="187"/>
-      <c r="B93" s="187"/>
-      <c r="C93" s="187"/>
-      <c r="D93" s="187"/>
-      <c r="E93" s="187"/>
+      <c r="A93" s="194"/>
+      <c r="B93" s="194"/>
+      <c r="C93" s="194"/>
+      <c r="D93" s="194"/>
+      <c r="E93" s="194"/>
     </row>
     <row r="95" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="23" t="s">
@@ -2749,7 +2761,7 @@
     </row>
     <row r="108" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="133" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B108" s="134">
         <v>-864378.73609999567</v>
@@ -2777,7 +2789,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="56" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B111" s="139">
         <f>B120</f>
@@ -2808,16 +2820,16 @@
     </row>
     <row r="115" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="188" t="s">
+      <c r="A116" s="195" t="s">
         <v>33</v>
       </c>
-      <c r="B116" s="188"/>
-      <c r="C116" s="188"/>
+      <c r="B116" s="195"/>
+      <c r="C116" s="195"/>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="188"/>
-      <c r="B117" s="188"/>
-      <c r="C117" s="188"/>
+      <c r="A117" s="195"/>
+      <c r="B117" s="195"/>
+      <c r="C117" s="195"/>
     </row>
     <row r="118" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="122"/>
@@ -2847,51 +2859,51 @@
       <c r="M121" s="8"/>
     </row>
     <row r="122" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="187"/>
-      <c r="B122" s="187"/>
-      <c r="C122" s="187"/>
-      <c r="D122" s="187"/>
-      <c r="E122" s="187"/>
+      <c r="A122" s="194"/>
+      <c r="B122" s="194"/>
+      <c r="C122" s="194"/>
+      <c r="D122" s="194"/>
+      <c r="E122" s="194"/>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="187"/>
-      <c r="B123" s="187"/>
-      <c r="C123" s="187"/>
-      <c r="D123" s="187"/>
-      <c r="E123" s="187"/>
+      <c r="A123" s="194"/>
+      <c r="B123" s="194"/>
+      <c r="C123" s="194"/>
+      <c r="D123" s="194"/>
+      <c r="E123" s="194"/>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="187"/>
-      <c r="B124" s="187"/>
-      <c r="C124" s="187"/>
-      <c r="D124" s="187"/>
-      <c r="E124" s="187"/>
+      <c r="A124" s="194"/>
+      <c r="B124" s="194"/>
+      <c r="C124" s="194"/>
+      <c r="D124" s="194"/>
+      <c r="E124" s="194"/>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="187"/>
-      <c r="B125" s="187"/>
-      <c r="C125" s="187"/>
-      <c r="D125" s="187"/>
-      <c r="E125" s="187"/>
+      <c r="A125" s="194"/>
+      <c r="B125" s="194"/>
+      <c r="C125" s="194"/>
+      <c r="D125" s="194"/>
+      <c r="E125" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A122:E125"/>
     <mergeCell ref="A116:C117"/>
     <mergeCell ref="A91:E93"/>
     <mergeCell ref="A75:B75"/>
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2927,15 +2939,15 @@
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
-      <c r="K1" s="202"/>
-      <c r="L1" s="202"/>
+      <c r="D1" s="196"/>
+      <c r="E1" s="196"/>
+      <c r="F1" s="196"/>
+      <c r="G1" s="196"/>
+      <c r="H1" s="196"/>
+      <c r="I1" s="196"/>
+      <c r="J1" s="196"/>
+      <c r="K1" s="196"/>
+      <c r="L1" s="196"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
@@ -2944,7 +2956,7 @@
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="165">
@@ -2954,7 +2966,7 @@
       <c r="H2" s="6"/>
       <c r="I2" s="7"/>
       <c r="J2" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K2" s="6"/>
       <c r="L2" s="132">
@@ -2981,46 +2993,46 @@
       <c r="N3" s="62"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="199" t="s">
+      <c r="A4" s="201" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="199" t="s">
+      <c r="B4" s="201" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="199" t="s">
+      <c r="C4" s="201" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="199" t="s">
+      <c r="D4" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="203" t="s">
+      <c r="E4" s="197" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="199" t="s">
+      <c r="F4" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="207" t="s">
+      <c r="G4" s="203" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="203" t="s">
+      <c r="H4" s="197" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="203" t="s">
+      <c r="I4" s="197" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="203" t="s">
+      <c r="J4" s="197" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="210" t="s">
-        <v>83</v>
+      <c r="K4" s="206" t="s">
+        <v>82</v>
       </c>
       <c r="L4" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="205" t="s">
+      <c r="M4" s="199" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="197" t="s">
+      <c r="N4" s="208" t="s">
         <v>37</v>
       </c>
       <c r="Q4" s="132">
@@ -3028,30 +3040,30 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="201"/>
-      <c r="B5" s="201"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="201"/>
-      <c r="E5" s="204"/>
-      <c r="F5" s="201"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="204"/>
-      <c r="K5" s="211"/>
+      <c r="A5" s="202"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="210"/>
+      <c r="D5" s="202"/>
+      <c r="E5" s="198"/>
+      <c r="F5" s="202"/>
+      <c r="G5" s="204"/>
+      <c r="H5" s="198"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="198"/>
+      <c r="K5" s="207"/>
       <c r="L5" s="63" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/02</v>
       </c>
-      <c r="M5" s="206"/>
-      <c r="N5" s="198"/>
+      <c r="M5" s="200"/>
+      <c r="N5" s="209"/>
     </row>
     <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="66">
         <v>1</v>
       </c>
       <c r="B6" s="66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" s="66"/>
       <c r="D6" s="75">
@@ -3105,7 +3117,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="66" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" s="67"/>
       <c r="D7" s="75">
@@ -3161,7 +3173,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" s="67"/>
       <c r="D8" s="75">
@@ -3215,7 +3227,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" s="67"/>
       <c r="D9" s="75">
@@ -3271,7 +3283,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10" s="67"/>
       <c r="D10" s="75">
@@ -3324,7 +3336,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="66" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" s="66"/>
       <c r="D11" s="75">
@@ -3379,7 +3391,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="66" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12" s="66"/>
       <c r="D12" s="75">
@@ -3431,7 +3443,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C13" s="67"/>
       <c r="D13" s="75">
@@ -3480,7 +3492,7 @@
         <v>0.08</v>
       </c>
       <c r="Q13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3489,7 +3501,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C14" s="67"/>
       <c r="D14" s="75">
@@ -3544,7 +3556,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15" s="67"/>
       <c r="D15" s="75">
@@ -3599,7 +3611,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C16" s="67"/>
       <c r="D16" s="75">
@@ -3654,7 +3666,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="66" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C17" s="67"/>
       <c r="D17" s="75">
@@ -3709,7 +3721,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C18" s="67"/>
       <c r="D18" s="75">
@@ -3764,7 +3776,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="66" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C19" s="67"/>
       <c r="D19" s="75">
@@ -3811,21 +3823,21 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="66">
+      <c r="A20" s="211">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="B20" s="66" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="67"/>
-      <c r="D20" s="75">
+      <c r="B20" s="211" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="212"/>
+      <c r="D20" s="213">
         <v>1.8</v>
       </c>
-      <c r="E20" s="76">
+      <c r="E20" s="214">
         <v>67402.149999999994</v>
       </c>
-      <c r="F20" s="77">
+      <c r="F20" s="214">
         <f>71572.15</f>
         <v>71572.149999999994</v>
       </c>
@@ -3871,7 +3883,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C21" s="66"/>
       <c r="D21" s="75">
@@ -3927,7 +3939,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C22" s="67"/>
       <c r="D22" s="75">
@@ -3981,7 +3993,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="66" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C23" s="131"/>
       <c r="D23" s="75">
@@ -4173,88 +4185,94 @@
     </row>
     <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="187" t="str">
+      <c r="B32" s="194" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="187"/>
-      <c r="D32" s="187"/>
-      <c r="E32" s="187"/>
-      <c r="F32" s="187"/>
-      <c r="G32" s="187"/>
-      <c r="H32" s="187"/>
-      <c r="I32" s="187"/>
-      <c r="J32" s="187"/>
-      <c r="K32" s="187"/>
-      <c r="L32" s="187"/>
+      <c r="C32" s="194"/>
+      <c r="D32" s="194"/>
+      <c r="E32" s="194"/>
+      <c r="F32" s="194"/>
+      <c r="G32" s="194"/>
+      <c r="H32" s="194"/>
+      <c r="I32" s="194"/>
+      <c r="J32" s="194"/>
+      <c r="K32" s="194"/>
+      <c r="L32" s="194"/>
     </row>
     <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="187"/>
-      <c r="C33" s="187"/>
-      <c r="D33" s="187"/>
-      <c r="E33" s="187"/>
-      <c r="F33" s="187"/>
-      <c r="G33" s="187"/>
-      <c r="H33" s="187"/>
-      <c r="I33" s="187"/>
-      <c r="J33" s="187"/>
-      <c r="K33" s="187"/>
-      <c r="L33" s="187"/>
+      <c r="B33" s="194"/>
+      <c r="C33" s="194"/>
+      <c r="D33" s="194"/>
+      <c r="E33" s="194"/>
+      <c r="F33" s="194"/>
+      <c r="G33" s="194"/>
+      <c r="H33" s="194"/>
+      <c r="I33" s="194"/>
+      <c r="J33" s="194"/>
+      <c r="K33" s="194"/>
+      <c r="L33" s="194"/>
     </row>
     <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="187"/>
-      <c r="C34" s="187"/>
-      <c r="D34" s="187"/>
-      <c r="E34" s="187"/>
-      <c r="F34" s="187"/>
-      <c r="G34" s="187"/>
-      <c r="H34" s="187"/>
-      <c r="I34" s="187"/>
-      <c r="J34" s="187"/>
-      <c r="K34" s="187"/>
-      <c r="L34" s="187"/>
+      <c r="B34" s="194"/>
+      <c r="C34" s="194"/>
+      <c r="D34" s="194"/>
+      <c r="E34" s="194"/>
+      <c r="F34" s="194"/>
+      <c r="G34" s="194"/>
+      <c r="H34" s="194"/>
+      <c r="I34" s="194"/>
+      <c r="J34" s="194"/>
+      <c r="K34" s="194"/>
+      <c r="L34" s="194"/>
     </row>
     <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="187"/>
-      <c r="C35" s="187"/>
-      <c r="D35" s="187"/>
-      <c r="E35" s="187"/>
-      <c r="F35" s="187"/>
-      <c r="G35" s="187"/>
-      <c r="H35" s="187"/>
-      <c r="I35" s="187"/>
-      <c r="J35" s="187"/>
-      <c r="K35" s="187"/>
-      <c r="L35" s="187"/>
+      <c r="B35" s="194"/>
+      <c r="C35" s="194"/>
+      <c r="D35" s="194"/>
+      <c r="E35" s="194"/>
+      <c r="F35" s="194"/>
+      <c r="G35" s="194"/>
+      <c r="H35" s="194"/>
+      <c r="I35" s="194"/>
+      <c r="J35" s="194"/>
+      <c r="K35" s="194"/>
+      <c r="L35" s="194"/>
     </row>
     <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="187"/>
-      <c r="C36" s="187"/>
-      <c r="D36" s="187"/>
-      <c r="E36" s="187"/>
-      <c r="F36" s="187"/>
-      <c r="G36" s="187"/>
-      <c r="H36" s="187"/>
-      <c r="I36" s="187"/>
-      <c r="J36" s="187"/>
-      <c r="K36" s="187"/>
-      <c r="L36" s="187"/>
+      <c r="B36" s="194"/>
+      <c r="C36" s="194"/>
+      <c r="D36" s="194"/>
+      <c r="E36" s="194"/>
+      <c r="F36" s="194"/>
+      <c r="G36" s="194"/>
+      <c r="H36" s="194"/>
+      <c r="I36" s="194"/>
+      <c r="J36" s="194"/>
+      <c r="K36" s="194"/>
+      <c r="L36" s="194"/>
     </row>
     <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="187"/>
-      <c r="C37" s="187"/>
-      <c r="D37" s="187"/>
-      <c r="E37" s="187"/>
-      <c r="F37" s="187"/>
-      <c r="G37" s="187"/>
-      <c r="H37" s="187"/>
-      <c r="I37" s="187"/>
-      <c r="J37" s="187"/>
-      <c r="K37" s="187"/>
-      <c r="L37" s="187"/>
+      <c r="B37" s="194"/>
+      <c r="C37" s="194"/>
+      <c r="D37" s="194"/>
+      <c r="E37" s="194"/>
+      <c r="F37" s="194"/>
+      <c r="G37" s="194"/>
+      <c r="H37" s="194"/>
+      <c r="I37" s="194"/>
+      <c r="J37" s="194"/>
+      <c r="K37" s="194"/>
+      <c r="L37" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="B32:L37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="E4:E5"/>
@@ -4264,12 +4282,6 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="B32:L37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4278,20 +4290,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
-  <dimension ref="C5:E5"/>
+  <dimension ref="C5:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C5" s="178" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" t="s">
-        <v>90</v>
-      </c>
+    <row r="5" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C5" s="215" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{44B2E0B3-0977-4FBD-9355-9C344C7DE166}"/>
+    <hyperlink ref="C5" r:id="rId1" display="laurasmiet@gmail.com" xr:uid="{44B2E0B3-0977-4FBD-9355-9C344C7DE166}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026/YRIGOYEN 7630/ENERO/YRIGOYEN7630-Enero.xlsx
+++ b/2026/YRIGOYEN 7630/ENERO/YRIGOYEN7630-Enero.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\YRIGOYEN 7630\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF07C49-090D-4BDA-8BED-CAD99B8E128C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC44A0F0-90D9-440A-9E65-12FAFF611666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -375,6 +375,9 @@
   </si>
   <si>
     <t>Le pusimos plata demas en enero 2026 a esta Sra.</t>
+  </si>
+  <si>
+    <t>Dice que abono $264.419,03 el 30/12 y que no le pusimos pago, adjunta su comprobante - Debe abonar $374.804,03.</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1094,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="217">
+  <cellXfs count="221">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1354,81 +1357,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1439,6 +1367,89 @@
     <xf numFmtId="44" fontId="21" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="3" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1805,21 +1816,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M125"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="15"/>
       <c r="B1" s="71" t="s">
         <v>55</v>
@@ -1828,7 +1839,7 @@
       <c r="D1" s="71"/>
       <c r="E1" s="72"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="73" t="s">
         <v>28</v>
@@ -1837,16 +1848,16 @@
       <c r="D2" s="73"/>
       <c r="E2" s="74"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16"/>
-      <c r="B3" s="188" t="s">
+      <c r="B3" s="198" t="s">
         <v>78</v>
       </c>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
-      <c r="E3" s="189"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="199"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
@@ -1857,7 +1868,7 @@
       <c r="D4" s="20"/>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>56</v>
       </c>
@@ -1870,7 +1881,7 @@
       </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>114</v>
       </c>
@@ -1881,57 +1892,57 @@
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="191" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="201" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="191"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="191"/>
-      <c r="C9" s="191"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="191"/>
-      <c r="C10" s="191"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="190" t="s">
+      <c r="C8" s="201"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="201"/>
+      <c r="C9" s="201"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="201"/>
+      <c r="C10" s="201"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="200" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="190"/>
-      <c r="C13" s="190"/>
-      <c r="D13" s="190"/>
-      <c r="E13" s="190"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="190"/>
-      <c r="B14" s="190"/>
-      <c r="C14" s="190"/>
-      <c r="D14" s="190"/>
-      <c r="E14" s="190"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="190"/>
-      <c r="B15" s="190"/>
-      <c r="C15" s="190"/>
-      <c r="D15" s="190"/>
-      <c r="E15" s="190"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="190"/>
-      <c r="B16" s="190"/>
-      <c r="C16" s="190"/>
-      <c r="D16" s="190"/>
-      <c r="E16" s="190"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="200"/>
+      <c r="C13" s="200"/>
+      <c r="D13" s="200"/>
+      <c r="E13" s="200"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="200"/>
+      <c r="B14" s="200"/>
+      <c r="C14" s="200"/>
+      <c r="D14" s="200"/>
+      <c r="E14" s="200"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="200"/>
+      <c r="B15" s="200"/>
+      <c r="C15" s="200"/>
+      <c r="D15" s="200"/>
+      <c r="E15" s="200"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="200"/>
+      <c r="B16" s="200"/>
+      <c r="C16" s="200"/>
+      <c r="D16" s="200"/>
+      <c r="E16" s="200"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>10</v>
       </c>
@@ -1940,7 +1951,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="36" t="s">
         <v>35</v>
       </c>
@@ -1949,7 +1960,7 @@
       <c r="D21" s="35"/>
       <c r="E21" s="35"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>75</v>
       </c>
@@ -1960,14 +1971,14 @@
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="158"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="59" t="s">
         <v>36</v>
       </c>
@@ -1980,7 +1991,7 @@
       <c r="E24" s="142"/>
       <c r="G24" s="22"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>45</v>
       </c>
@@ -1989,28 +2000,28 @@
       <c r="D25" s="158"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="29"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="158"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="158"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="168"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>40</v>
       </c>
@@ -2019,7 +2030,7 @@
       <c r="D29" s="168"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="59" t="s">
         <v>36</v>
       </c>
@@ -2031,7 +2042,7 @@
       </c>
       <c r="E30" s="142"/>
     </row>
-    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="30" t="s">
         <v>1</v>
       </c>
@@ -2044,7 +2055,7 @@
       </c>
       <c r="F31" s="22"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="36" t="s">
         <v>19</v>
       </c>
@@ -2053,18 +2064,18 @@
       <c r="D32" s="171"/>
       <c r="E32" s="144"/>
     </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="186" t="s">
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="196" t="s">
         <v>98</v>
       </c>
-      <c r="B33" s="187"/>
+      <c r="B33" s="197"/>
       <c r="C33" s="54"/>
       <c r="D33" s="158">
         <v>35000</v>
       </c>
       <c r="E33" s="145"/>
     </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="178" t="s">
         <v>102</v>
       </c>
@@ -2075,11 +2086,11 @@
       </c>
       <c r="E34" s="145"/>
     </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="186" t="s">
+    <row r="35" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="196" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="187"/>
+      <c r="B35" s="197"/>
       <c r="C35" s="54"/>
       <c r="D35" s="181">
         <v>147300</v>
@@ -2089,7 +2100,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="30" t="s">
         <v>16</v>
       </c>
@@ -2101,7 +2112,7 @@
         <v>294300</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="36" t="s">
         <v>32</v>
       </c>
@@ -2110,11 +2121,11 @@
       <c r="D37" s="173"/>
       <c r="E37" s="147"/>
     </row>
-    <row r="38" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="192" t="s">
+    <row r="38" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="194" t="s">
         <v>90</v>
       </c>
-      <c r="B38" s="193"/>
+      <c r="B38" s="195"/>
       <c r="C38" s="56"/>
       <c r="D38" s="182">
         <f>6696+26570</f>
@@ -2124,11 +2135,11 @@
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="186" t="s">
+    <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="196" t="s">
         <v>91</v>
       </c>
-      <c r="B39" s="187"/>
+      <c r="B39" s="197"/>
       <c r="C39" s="56"/>
       <c r="D39" s="183">
         <v>54278</v>
@@ -2138,7 +2149,7 @@
         <v>Debito 5/1</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="30" t="s">
         <v>2</v>
       </c>
@@ -2150,7 +2161,7 @@
         <v>87544</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="36" t="s">
         <v>17</v>
       </c>
@@ -2159,7 +2170,7 @@
       <c r="D41" s="174"/>
       <c r="E41" s="151"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>48</v>
       </c>
@@ -2173,7 +2184,7 @@
       </c>
       <c r="G42" s="126"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>79</v>
       </c>
@@ -2186,7 +2197,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>79</v>
       </c>
@@ -2205,7 +2216,7 @@
       </c>
       <c r="G44" s="141"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>99</v>
       </c>
@@ -2218,7 +2229,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="str">
         <f>A45</f>
         <v>Sindicatos mes de ENERO</v>
@@ -2233,7 +2244,7 @@
         <v>Debito 13/01</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="str">
         <f>A46</f>
         <v>Sindicatos mes de ENERO</v>
@@ -2248,7 +2259,7 @@
         <v>Debito 13/01</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="30" t="s">
         <v>3</v>
       </c>
@@ -2260,7 +2271,7 @@
         <v>1241022.82</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="36" t="s">
         <v>18</v>
       </c>
@@ -2269,7 +2280,7 @@
       <c r="D49" s="174"/>
       <c r="E49" s="151"/>
     </row>
-    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>77</v>
       </c>
@@ -2282,7 +2293,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>81</v>
       </c>
@@ -2295,7 +2306,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>80</v>
       </c>
@@ -2308,11 +2319,11 @@
         <v>107</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="192" t="s">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="194" t="s">
         <v>76</v>
       </c>
-      <c r="B53" s="193"/>
+      <c r="B53" s="195"/>
       <c r="C53" s="5"/>
       <c r="D53" s="162">
         <v>377536.65</v>
@@ -2321,7 +2332,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="30" t="s">
         <v>4</v>
       </c>
@@ -2333,14 +2344,14 @@
         <v>523875.18000000005</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="36"/>
       <c r="B55" s="30"/>
       <c r="C55" s="30"/>
       <c r="D55" s="172"/>
       <c r="E55" s="152"/>
     </row>
-    <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="164" t="s">
         <v>92</v>
       </c>
@@ -2353,7 +2364,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="164" t="s">
         <v>100</v>
       </c>
@@ -2366,7 +2377,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="164" t="s">
         <v>112</v>
       </c>
@@ -2379,7 +2390,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="164" t="s">
         <v>110</v>
       </c>
@@ -2392,11 +2403,11 @@
         <v>109</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="192" t="s">
+    <row r="60" spans="1:5" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="194" t="s">
         <v>111</v>
       </c>
-      <c r="B60" s="193"/>
+      <c r="B60" s="195"/>
       <c r="C60" s="5"/>
       <c r="D60" s="108">
         <v>35500</v>
@@ -2405,11 +2416,11 @@
         <v>109</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="192" t="s">
+    <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="194" t="s">
         <v>108</v>
       </c>
-      <c r="B61" s="193"/>
+      <c r="B61" s="195"/>
       <c r="C61" s="5"/>
       <c r="D61" s="108">
         <v>45000</v>
@@ -2418,7 +2429,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="30" t="s">
         <v>9</v>
       </c>
@@ -2430,7 +2441,7 @@
         <v>610100</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="36" t="s">
         <v>12</v>
       </c>
@@ -2439,7 +2450,7 @@
       <c r="D63" s="170"/>
       <c r="E63" s="152"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>89</v>
       </c>
@@ -2450,7 +2461,7 @@
       </c>
       <c r="E64" s="154"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>88</v>
       </c>
@@ -2461,7 +2472,7 @@
       </c>
       <c r="E65" s="41"/>
     </row>
-    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="53" t="s">
         <v>16</v>
       </c>
@@ -2473,14 +2484,14 @@
         <v>141932.56</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
       <c r="D67" s="104"/>
       <c r="E67" s="112"/>
     </row>
-    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="31" t="s">
         <v>51</v>
       </c>
@@ -2489,13 +2500,13 @@
       <c r="D68" s="113"/>
       <c r="E68" s="114"/>
     </row>
-    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="D69" s="115"/>
       <c r="E69" s="116"/>
       <c r="F69" s="45"/>
     </row>
-    <row r="70" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>13</v>
       </c>
@@ -2514,7 +2525,7 @@
       <c r="K70" s="126"/>
       <c r="L70" s="126"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D71" s="115"/>
       <c r="E71" s="115"/>
       <c r="H71" s="126"/>
@@ -2523,12 +2534,12 @@
       <c r="K71" s="126"/>
       <c r="L71" s="126"/>
     </row>
-    <row r="72" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D72" s="115"/>
       <c r="E72" s="115"/>
       <c r="H72" s="177"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
         <v>46</v>
       </c>
@@ -2537,35 +2548,35 @@
       <c r="D73" s="119"/>
       <c r="E73" s="120"/>
     </row>
-    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="192"/>
-      <c r="B74" s="193"/>
+    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="194"/>
+      <c r="B74" s="195"/>
       <c r="C74" s="5"/>
       <c r="D74" s="130"/>
       <c r="E74" s="106"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="192"/>
-      <c r="B75" s="193"/>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" s="194"/>
+      <c r="B75" s="195"/>
       <c r="C75" s="5"/>
       <c r="D75" s="108"/>
       <c r="E75" s="106"/>
     </row>
-    <row r="76" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="186"/>
-      <c r="B76" s="187"/>
+    <row r="76" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="196"/>
+      <c r="B76" s="197"/>
       <c r="C76" s="5"/>
       <c r="D76" s="108"/>
       <c r="E76" s="106"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="107"/>
       <c r="B77" s="109"/>
       <c r="C77" s="5"/>
       <c r="D77" s="108"/>
       <c r="E77" s="106"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="51"/>
       <c r="B78" s="50"/>
       <c r="C78" s="50"/>
@@ -2575,9 +2586,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="31" t="s">
         <v>20</v>
       </c>
@@ -2586,8 +2597,8 @@
       <c r="D81" s="32"/>
       <c r="E81" s="103"/>
     </row>
-    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>21</v>
       </c>
@@ -2599,8 +2610,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="101" t="s">
         <v>14</v>
       </c>
@@ -2609,7 +2620,7 @@
         <v>3770619.5600000005</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="101" t="s">
         <v>15</v>
       </c>
@@ -2618,7 +2629,7 @@
         <v>3770619.5600000005</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="101" t="s">
         <v>22</v>
       </c>
@@ -2627,7 +2638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="101" t="s">
         <v>41</v>
       </c>
@@ -2636,44 +2647,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="194"/>
-      <c r="B91" s="194"/>
-      <c r="C91" s="194"/>
-      <c r="D91" s="194"/>
-      <c r="E91" s="194"/>
-    </row>
-    <row r="92" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="194"/>
-      <c r="B92" s="194"/>
-      <c r="C92" s="194"/>
-      <c r="D92" s="194"/>
-      <c r="E92" s="194"/>
-    </row>
-    <row r="93" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="194"/>
-      <c r="B93" s="194"/>
-      <c r="C93" s="194"/>
-      <c r="D93" s="194"/>
-      <c r="E93" s="194"/>
-    </row>
-    <row r="95" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="192"/>
+      <c r="B91" s="192"/>
+      <c r="C91" s="192"/>
+      <c r="D91" s="192"/>
+      <c r="E91" s="192"/>
+    </row>
+    <row r="92" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="192"/>
+      <c r="B92" s="192"/>
+      <c r="C92" s="192"/>
+      <c r="D92" s="192"/>
+      <c r="E92" s="192"/>
+    </row>
+    <row r="93" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="192"/>
+      <c r="B93" s="192"/>
+      <c r="C93" s="192"/>
+      <c r="D93" s="192"/>
+      <c r="E93" s="192"/>
+    </row>
+    <row r="95" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="23" t="s">
         <v>34</v>
       </c>
       <c r="B95" s="127"/>
       <c r="C95" s="24"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="34"/>
       <c r="B96" s="61">
         <v>0</v>
       </c>
       <c r="C96" s="26"/>
     </row>
-    <row r="97" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="25" t="s">
         <v>7</v>
       </c>
@@ -2683,14 +2694,14 @@
       </c>
       <c r="C97" s="24"/>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="25"/>
       <c r="B98" s="41">
         <v>0</v>
       </c>
       <c r="C98" s="24"/>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="25" t="s">
         <v>42</v>
       </c>
@@ -2700,19 +2711,19 @@
       </c>
       <c r="C99" s="24"/>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="28"/>
       <c r="B100" s="49"/>
       <c r="C100" s="24"/>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="125" t="s">
         <v>47</v>
       </c>
       <c r="B101" s="49"/>
       <c r="C101" s="24"/>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="40" t="s">
         <v>23</v>
       </c>
@@ -2722,7 +2733,7 @@
       </c>
       <c r="C102" s="24"/>
     </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="28" t="s">
         <v>24</v>
       </c>
@@ -2732,7 +2743,7 @@
       </c>
       <c r="C103" s="24"/>
     </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="33" t="s">
         <v>9</v>
       </c>
@@ -2743,23 +2754,23 @@
       <c r="C104" s="27"/>
       <c r="D104" s="45"/>
     </row>
-    <row r="105" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="42"/>
       <c r="C105" s="27"/>
       <c r="D105" s="45"/>
       <c r="E105" s="128"/>
       <c r="F105" s="129"/>
     </row>
-    <row r="106" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="43"/>
       <c r="C106" s="27"/>
     </row>
-    <row r="107" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107"/>
       <c r="B107" s="42"/>
       <c r="C107" s="38"/>
     </row>
-    <row r="108" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="133" t="s">
         <v>87</v>
       </c>
@@ -2769,7 +2780,7 @@
       <c r="C108" s="38"/>
       <c r="D108" s="48"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="56" t="s">
         <v>52</v>
       </c>
@@ -2778,7 +2789,7 @@
         <v>-3770619.5600000005</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="56" t="s">
         <v>53</v>
       </c>
@@ -2787,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="56" t="s">
         <v>85</v>
       </c>
@@ -2796,7 +2807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="56" t="s">
         <v>54</v>
       </c>
@@ -2805,7 +2816,7 @@
         <v>3225298.1600000006</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="137" t="s">
         <v>49</v>
       </c>
@@ -2814,24 +2825,24 @@
         <v>-1409700.1360999956</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="135"/>
       <c r="B114" s="135"/>
     </row>
-    <row r="115" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="195" t="s">
+    <row r="115" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A116" s="193" t="s">
         <v>33</v>
       </c>
-      <c r="B116" s="195"/>
-      <c r="C116" s="195"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="195"/>
-      <c r="B117" s="195"/>
-      <c r="C117" s="195"/>
-    </row>
-    <row r="118" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B116" s="193"/>
+      <c r="C116" s="193"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A117" s="193"/>
+      <c r="B117" s="193"/>
+      <c r="C117" s="193"/>
+    </row>
+    <row r="118" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="122"/>
       <c r="B118" s="37"/>
       <c r="C118" s="37">
@@ -2839,13 +2850,13 @@
       </c>
       <c r="E118" s="141"/>
     </row>
-    <row r="119" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="122"/>
       <c r="B119" s="124"/>
       <c r="C119" s="121"/>
       <c r="D119" s="141"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="46" t="s">
         <v>9</v>
       </c>
@@ -2855,55 +2866,55 @@
       </c>
       <c r="C120" s="47"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M121" s="8"/>
     </row>
-    <row r="122" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="194"/>
-      <c r="B122" s="194"/>
-      <c r="C122" s="194"/>
-      <c r="D122" s="194"/>
-      <c r="E122" s="194"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="194"/>
-      <c r="B123" s="194"/>
-      <c r="C123" s="194"/>
-      <c r="D123" s="194"/>
-      <c r="E123" s="194"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="194"/>
-      <c r="B124" s="194"/>
-      <c r="C124" s="194"/>
-      <c r="D124" s="194"/>
-      <c r="E124" s="194"/>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="194"/>
-      <c r="B125" s="194"/>
-      <c r="C125" s="194"/>
-      <c r="D125" s="194"/>
-      <c r="E125" s="194"/>
+    <row r="122" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="192"/>
+      <c r="B122" s="192"/>
+      <c r="C122" s="192"/>
+      <c r="D122" s="192"/>
+      <c r="E122" s="192"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A123" s="192"/>
+      <c r="B123" s="192"/>
+      <c r="C123" s="192"/>
+      <c r="D123" s="192"/>
+      <c r="E123" s="192"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A124" s="192"/>
+      <c r="B124" s="192"/>
+      <c r="C124" s="192"/>
+      <c r="D124" s="192"/>
+      <c r="E124" s="192"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A125" s="192"/>
+      <c r="B125" s="192"/>
+      <c r="C125" s="192"/>
+      <c r="D125" s="192"/>
+      <c r="E125" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A122:E125"/>
     <mergeCell ref="A116:C117"/>
     <mergeCell ref="A91:E93"/>
     <mergeCell ref="A75:B75"/>
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2914,44 +2925,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="0.28515625" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" customWidth="1"/>
-    <col min="9" max="9" width="0.140625" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.33203125" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
+    <col min="9" max="9" width="0.109375" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" customWidth="1"/>
     <col min="13" max="13" width="12" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" customWidth="1"/>
-    <col min="15" max="15" width="0.140625" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" customWidth="1"/>
+    <col min="15" max="15" width="0.109375" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="196"/>
-      <c r="E1" s="196"/>
-      <c r="F1" s="196"/>
-      <c r="G1" s="196"/>
-      <c r="H1" s="196"/>
-      <c r="I1" s="196"/>
-      <c r="J1" s="196"/>
-      <c r="K1" s="196"/>
-      <c r="L1" s="196"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2976,7 +2987,7 @@
       <c r="N2" s="57"/>
       <c r="O2" s="22"/>
     </row>
-    <row r="3" spans="1:17" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -2992,73 +3003,73 @@
       <c r="M3" s="58"/>
       <c r="N3" s="62"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="201" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="204" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="201" t="s">
+      <c r="B4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="201" t="s">
+      <c r="C4" s="204" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="201" t="s">
+      <c r="D4" s="204" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="208" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="201" t="s">
+      <c r="F4" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="203" t="s">
+      <c r="G4" s="212" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="197" t="s">
+      <c r="H4" s="208" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="197" t="s">
+      <c r="I4" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="197" t="s">
+      <c r="J4" s="208" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="206" t="s">
+      <c r="K4" s="215" t="s">
         <v>82</v>
       </c>
       <c r="L4" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="199" t="s">
+      <c r="M4" s="210" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="208" t="s">
+      <c r="N4" s="202" t="s">
         <v>37</v>
       </c>
       <c r="Q4" s="132">
         <v>3774269.17</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="202"/>
-      <c r="B5" s="202"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="202"/>
-      <c r="E5" s="198"/>
-      <c r="F5" s="202"/>
-      <c r="G5" s="204"/>
-      <c r="H5" s="198"/>
-      <c r="I5" s="205"/>
-      <c r="J5" s="198"/>
-      <c r="K5" s="207"/>
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="205"/>
+      <c r="D5" s="206"/>
+      <c r="E5" s="209"/>
+      <c r="F5" s="206"/>
+      <c r="G5" s="213"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="214"/>
+      <c r="J5" s="209"/>
+      <c r="K5" s="216"/>
       <c r="L5" s="63" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/02</v>
       </c>
-      <c r="M5" s="200"/>
-      <c r="N5" s="209"/>
-    </row>
-    <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" s="211"/>
+      <c r="N5" s="203"/>
+    </row>
+    <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="66">
         <v>1</v>
       </c>
@@ -3111,7 +3122,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="66">
         <f>A6+1</f>
         <v>2</v>
@@ -3167,22 +3178,22 @@
       </c>
       <c r="P7" s="45"/>
     </row>
-    <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="66">
+    <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="217">
         <f t="shared" ref="A8:A23" si="7">A7+1</f>
         <v>3</v>
       </c>
-      <c r="B8" s="66" t="s">
+      <c r="B8" s="217" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="67"/>
-      <c r="D8" s="75">
+      <c r="C8" s="218"/>
+      <c r="D8" s="219">
         <v>6.65</v>
       </c>
-      <c r="E8" s="76">
+      <c r="E8" s="220">
         <v>536769.03</v>
       </c>
-      <c r="F8" s="77">
+      <c r="F8" s="220">
         <v>150000.03</v>
       </c>
       <c r="G8" s="78">
@@ -3221,7 +3232,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="66">
         <f t="shared" si="7"/>
         <v>4</v>
@@ -3277,7 +3288,7 @@
       </c>
       <c r="Q9" s="45"/>
     </row>
-    <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="66">
         <f t="shared" si="7"/>
         <v>5</v>
@@ -3330,7 +3341,7 @@
       </c>
       <c r="Q10" s="45"/>
     </row>
-    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="66">
         <f t="shared" si="7"/>
         <v>6</v>
@@ -3385,7 +3396,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="66">
         <f t="shared" si="7"/>
         <v>7</v>
@@ -3437,7 +3448,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="66">
         <f t="shared" si="7"/>
         <v>8</v>
@@ -3495,7 +3506,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="66">
         <f t="shared" si="7"/>
         <v>9</v>
@@ -3550,7 +3561,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="66">
         <f t="shared" si="7"/>
         <v>10</v>
@@ -3605,7 +3616,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="66">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -3660,7 +3671,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="66">
         <f t="shared" si="7"/>
         <v>12</v>
@@ -3715,7 +3726,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="66">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -3770,7 +3781,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="66">
         <f t="shared" si="7"/>
         <v>14</v>
@@ -3822,22 +3833,22 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="211">
+    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="186">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="B20" s="211" t="s">
+      <c r="B20" s="186" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="212"/>
-      <c r="D20" s="213">
+      <c r="C20" s="187"/>
+      <c r="D20" s="188">
         <v>1.8</v>
       </c>
-      <c r="E20" s="214">
+      <c r="E20" s="189">
         <v>67402.149999999994</v>
       </c>
-      <c r="F20" s="214">
+      <c r="F20" s="189">
         <f>71572.15</f>
         <v>71572.149999999994</v>
       </c>
@@ -3877,7 +3888,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="66">
         <f t="shared" si="7"/>
         <v>16</v>
@@ -3933,7 +3944,7 @@
       </c>
       <c r="Q21" s="44"/>
     </row>
-    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="66">
         <f t="shared" si="7"/>
         <v>17</v>
@@ -3987,7 +3998,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="66">
         <f t="shared" si="7"/>
         <v>18</v>
@@ -4042,7 +4053,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="66"/>
       <c r="B24" s="66"/>
       <c r="C24" s="67"/>
@@ -4062,7 +4073,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="85"/>
       <c r="B25" s="66"/>
       <c r="C25" s="67"/>
@@ -4079,7 +4090,7 @@
       <c r="N25" s="84"/>
       <c r="O25" s="45"/>
     </row>
-    <row r="26" spans="1:17" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="85"/>
       <c r="B26" s="68"/>
       <c r="C26" s="67"/>
@@ -4096,7 +4107,7 @@
       <c r="N26" s="84"/>
       <c r="O26" s="45"/>
     </row>
-    <row r="27" spans="1:17" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="86"/>
       <c r="B27" s="66"/>
       <c r="C27" s="67"/>
@@ -4113,7 +4124,7 @@
       <c r="N27" s="84"/>
       <c r="O27" s="45"/>
     </row>
-    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="66"/>
       <c r="B28" s="92"/>
       <c r="C28" s="92"/>
@@ -4130,7 +4141,7 @@
       <c r="N28" s="95"/>
       <c r="O28" s="45"/>
     </row>
-    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="96"/>
       <c r="B29" s="97"/>
       <c r="C29" s="97"/>
@@ -4179,100 +4190,94 @@
         <v>6639695.71</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="52"/>
       <c r="C30" s="52"/>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="194" t="str">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="192" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="194"/>
-      <c r="D32" s="194"/>
-      <c r="E32" s="194"/>
-      <c r="F32" s="194"/>
-      <c r="G32" s="194"/>
-      <c r="H32" s="194"/>
-      <c r="I32" s="194"/>
-      <c r="J32" s="194"/>
-      <c r="K32" s="194"/>
-      <c r="L32" s="194"/>
-    </row>
-    <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="194"/>
-      <c r="C33" s="194"/>
-      <c r="D33" s="194"/>
-      <c r="E33" s="194"/>
-      <c r="F33" s="194"/>
-      <c r="G33" s="194"/>
-      <c r="H33" s="194"/>
-      <c r="I33" s="194"/>
-      <c r="J33" s="194"/>
-      <c r="K33" s="194"/>
-      <c r="L33" s="194"/>
-    </row>
-    <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="194"/>
-      <c r="C34" s="194"/>
-      <c r="D34" s="194"/>
-      <c r="E34" s="194"/>
-      <c r="F34" s="194"/>
-      <c r="G34" s="194"/>
-      <c r="H34" s="194"/>
-      <c r="I34" s="194"/>
-      <c r="J34" s="194"/>
-      <c r="K34" s="194"/>
-      <c r="L34" s="194"/>
-    </row>
-    <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="194"/>
-      <c r="C35" s="194"/>
-      <c r="D35" s="194"/>
-      <c r="E35" s="194"/>
-      <c r="F35" s="194"/>
-      <c r="G35" s="194"/>
-      <c r="H35" s="194"/>
-      <c r="I35" s="194"/>
-      <c r="J35" s="194"/>
-      <c r="K35" s="194"/>
-      <c r="L35" s="194"/>
-    </row>
-    <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="194"/>
-      <c r="C36" s="194"/>
-      <c r="D36" s="194"/>
-      <c r="E36" s="194"/>
-      <c r="F36" s="194"/>
-      <c r="G36" s="194"/>
-      <c r="H36" s="194"/>
-      <c r="I36" s="194"/>
-      <c r="J36" s="194"/>
-      <c r="K36" s="194"/>
-      <c r="L36" s="194"/>
-    </row>
-    <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="194"/>
-      <c r="C37" s="194"/>
-      <c r="D37" s="194"/>
-      <c r="E37" s="194"/>
-      <c r="F37" s="194"/>
-      <c r="G37" s="194"/>
-      <c r="H37" s="194"/>
-      <c r="I37" s="194"/>
-      <c r="J37" s="194"/>
-      <c r="K37" s="194"/>
-      <c r="L37" s="194"/>
+      <c r="C32" s="192"/>
+      <c r="D32" s="192"/>
+      <c r="E32" s="192"/>
+      <c r="F32" s="192"/>
+      <c r="G32" s="192"/>
+      <c r="H32" s="192"/>
+      <c r="I32" s="192"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="192"/>
+      <c r="L32" s="192"/>
+    </row>
+    <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="192"/>
+      <c r="C33" s="192"/>
+      <c r="D33" s="192"/>
+      <c r="E33" s="192"/>
+      <c r="F33" s="192"/>
+      <c r="G33" s="192"/>
+      <c r="H33" s="192"/>
+      <c r="I33" s="192"/>
+      <c r="J33" s="192"/>
+      <c r="K33" s="192"/>
+      <c r="L33" s="192"/>
+    </row>
+    <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="192"/>
+      <c r="C34" s="192"/>
+      <c r="D34" s="192"/>
+      <c r="E34" s="192"/>
+      <c r="F34" s="192"/>
+      <c r="G34" s="192"/>
+      <c r="H34" s="192"/>
+      <c r="I34" s="192"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="192"/>
+      <c r="L34" s="192"/>
+    </row>
+    <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="192"/>
+      <c r="C35" s="192"/>
+      <c r="D35" s="192"/>
+      <c r="E35" s="192"/>
+      <c r="F35" s="192"/>
+      <c r="G35" s="192"/>
+      <c r="H35" s="192"/>
+      <c r="I35" s="192"/>
+      <c r="J35" s="192"/>
+      <c r="K35" s="192"/>
+      <c r="L35" s="192"/>
+    </row>
+    <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="192"/>
+      <c r="C36" s="192"/>
+      <c r="D36" s="192"/>
+      <c r="E36" s="192"/>
+      <c r="F36" s="192"/>
+      <c r="G36" s="192"/>
+      <c r="H36" s="192"/>
+      <c r="I36" s="192"/>
+      <c r="J36" s="192"/>
+      <c r="K36" s="192"/>
+      <c r="L36" s="192"/>
+    </row>
+    <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="192"/>
+      <c r="C37" s="192"/>
+      <c r="D37" s="192"/>
+      <c r="E37" s="192"/>
+      <c r="F37" s="192"/>
+      <c r="G37" s="192"/>
+      <c r="H37" s="192"/>
+      <c r="I37" s="192"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="192"/>
+      <c r="L37" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="B32:L37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="E4:E5"/>
@@ -4282,6 +4287,12 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="B32:L37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4290,17 +4301,30 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
-  <dimension ref="C5:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C5:K8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C5" s="215" t="s">
+    <row r="5" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C5" s="190" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="216"/>
-      <c r="E5" s="216"/>
-      <c r="F5" s="216"/>
-      <c r="G5" s="216"/>
+      <c r="D5" s="191"/>
+      <c r="E5" s="191"/>
+      <c r="F5" s="191"/>
+      <c r="G5" s="191"/>
+    </row>
+    <row r="8" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C8" s="156" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="156"/>
+      <c r="E8" s="156"/>
+      <c r="F8" s="156"/>
+      <c r="G8" s="156"/>
+      <c r="H8" s="156"/>
+      <c r="I8" s="156"/>
+      <c r="J8" s="156"/>
+      <c r="K8" s="156"/>
     </row>
   </sheetData>
   <hyperlinks>
